--- a/jamaica/budget_layer_all_years.xlsx
+++ b/jamaica/budget_layer_all_years.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J421"/>
+  <dimension ref="A1:M421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,21 @@
           <t>source_file</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>programme_class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>class_source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>strategy_name_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +520,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +567,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,6 +622,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,6 +677,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -685,6 +732,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -730,6 +787,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -765,6 +832,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -810,6 +879,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -855,6 +934,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -890,6 +979,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -935,6 +1026,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -980,6 +1081,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1015,6 +1126,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1060,6 +1173,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1105,6 +1228,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1150,6 +1283,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1185,6 +1328,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1199,7 +1344,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Registrar General's Department and Island Records Office</t>
+          <t>Registrar General's Department and Island Records</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1220,6 +1365,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Registrar General's Department and Island Records Office</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1265,6 +1417,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1310,6 +1472,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1324,7 +1496,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Office of the Cabinet" --&gt;</t>
+          <t>Office of the Cabinet</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1355,6 +1527,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Office of the Cabinet" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1390,6 +1577,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1435,6 +1624,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1480,6 +1679,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1515,6 +1724,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1560,6 +1771,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1605,6 +1826,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1640,6 +1871,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1685,6 +1918,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1730,6 +1973,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1775,6 +2028,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1820,6 +2083,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1865,6 +2138,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1910,6 +2193,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1955,6 +2248,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2000,6 +2303,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2045,6 +2358,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2090,6 +2413,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2135,6 +2468,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2180,6 +2523,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2225,6 +2578,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2260,6 +2623,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2305,6 +2670,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2350,6 +2725,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2395,6 +2780,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2440,6 +2835,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2485,6 +2890,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2530,6 +2945,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2575,6 +3000,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2620,6 +3055,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2665,6 +3110,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2700,6 +3155,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2745,6 +3202,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2790,6 +3257,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2804,7 +3281,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2825,6 +3302,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2870,6 +3354,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2915,6 +3409,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2960,6 +3464,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3005,6 +3519,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3050,6 +3574,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3064,7 +3598,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3095,6 +3629,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3109,7 +3658,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3140,6 +3689,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3154,7 +3718,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3185,6 +3749,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3199,7 +3778,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3230,6 +3809,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3265,6 +3859,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3300,6 +3896,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3345,6 +3943,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3390,6 +3998,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3425,6 +4043,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3439,7 +4059,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ministry of Justice" --&gt;</t>
+          <t>Ministry of Justice</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3460,6 +4080,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Ministry of Justice" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3505,6 +4132,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3550,6 +4187,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3564,7 +4211,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ministry of Justice" --&gt;</t>
+          <t>Ministry of Justice</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3595,6 +4242,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Ministry of Justice" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3630,6 +4292,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3675,6 +4339,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3720,6 +4394,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3765,6 +4449,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3810,6 +4504,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3855,6 +4559,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3890,6 +4604,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3904,7 +4620,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information.</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3925,6 +4641,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3939,7 +4662,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3970,6 +4693,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3984,7 +4722,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4015,6 +4753,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4029,7 +4782,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4060,6 +4813,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4074,7 +4842,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4105,6 +4873,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4119,7 +4902,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4150,6 +4933,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4164,7 +4962,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4195,6 +4993,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4209,7 +5022,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4240,6 +5053,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4254,7 +5082,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4285,6 +5113,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4299,7 +5142,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4330,6 +5173,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4344,7 +5202,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4375,6 +5233,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4389,7 +5262,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4420,6 +5293,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4434,7 +5322,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4465,6 +5353,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4479,7 +5382,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4510,6 +5413,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4524,7 +5442,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4555,6 +5473,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4569,7 +5502,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4600,6 +5533,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4614,7 +5562,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4645,6 +5593,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4659,7 +5622,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ministry of Education, Youth and Information</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4690,6 +5653,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Ministry of Education, Youth and Information</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4704,7 +5682,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ministry of Health</t>
+          <t>Ministry of Health and Wellness</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4735,6 +5713,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Ministry of Health</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4749,7 +5742,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ministry of Culture, Gender, Entertainment and Sport" --&gt;</t>
+          <t>Ministry of Culture, Gender, Entertainment and Sport</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4780,6 +5773,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Ministry of Culture, Gender, Entertainment and Sport" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4815,6 +5823,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4850,6 +5860,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4895,6 +5907,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4930,6 +5952,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4975,6 +5999,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5020,6 +6054,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5034,7 +6078,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ministry of Local Government and Community Development" --&gt;</t>
+          <t>Ministry of Local Government and Community</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5055,6 +6099,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Ministry of Local Government and Community Development" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5100,6 +6151,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5135,6 +6196,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5180,6 +6243,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5225,6 +6298,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5270,6 +6353,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5315,6 +6408,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5360,6 +6463,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5405,6 +6518,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5440,6 +6563,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5485,6 +6610,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5530,6 +6665,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5575,6 +6720,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5620,6 +6775,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5665,6 +6830,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5710,6 +6885,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5755,6 +6940,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5790,6 +6985,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5835,6 +7032,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5880,6 +7087,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5915,6 +7132,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5960,6 +7179,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6005,6 +7234,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6040,6 +7279,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6085,6 +7326,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6130,6 +7381,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6165,6 +7426,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6210,6 +7473,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6255,6 +7528,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6269,7 +7552,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Registrar General's Department and Island Records Office</t>
+          <t>Registrar General's Department and Island Records</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6290,6 +7573,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Registrar General's Department and Island Records Office</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6335,6 +7625,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6380,6 +7680,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6425,6 +7735,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6460,6 +7780,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6505,6 +7827,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6550,6 +7882,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6564,7 +7906,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ministry of Tourism Budget 1 - Recurrent Function 04 - Economic Affairs SubFunction 13 - Tourism Programme 652 - Tourism Development" --&gt;</t>
+          <t>Ministry of Tourism</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6585,6 +7927,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Ministry of Tourism Budget 1 - Recurrent Function 04 - Economic Affairs SubFunction 13 - Tourism Programme 652 - Tourism Development" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6620,6 +7969,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6665,6 +8016,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6710,6 +8071,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6755,6 +8126,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6800,6 +8181,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6845,6 +8236,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6890,6 +8291,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6925,6 +8336,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6970,6 +8383,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7015,6 +8438,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7050,6 +8483,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7095,6 +8530,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7140,6 +8585,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7185,6 +8640,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7220,6 +8685,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7265,6 +8732,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7310,6 +8787,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7345,6 +8832,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7359,7 +8848,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7390,6 +8879,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7404,7 +8908,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7435,6 +8939,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7449,7 +8968,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7480,6 +8999,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7494,7 +9028,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7525,6 +9059,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7539,7 +9088,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7570,6 +9119,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7584,7 +9148,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7615,6 +9179,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7629,7 +9208,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7660,6 +9239,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7705,6 +9299,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7750,6 +9354,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7795,6 +9409,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7840,6 +9464,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7885,6 +9519,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7930,6 +9574,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7975,6 +9629,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8020,6 +9684,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8065,6 +9739,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8079,7 +9763,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8100,6 +9784,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8145,6 +9836,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8190,6 +9891,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8235,6 +9946,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8249,7 +9970,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8280,6 +10001,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8294,7 +10030,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8325,6 +10061,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8339,7 +10090,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8370,6 +10121,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8405,6 +10171,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8450,6 +10218,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8495,6 +10273,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8530,6 +10318,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8575,6 +10365,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8610,6 +10410,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8624,7 +10426,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Passport, Immigration and Citizenship Agency Budget 1 - Recurrent</t>
+          <t>Passport, Immigration and Citizenship Agency</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8655,6 +10457,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Passport, Immigration and Citizenship Agency Budget 1 - Recurrent</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8669,7 +10486,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Passport, Immigration and Citizenship Agency Budget 1 - Recurrent</t>
+          <t>Passport, Immigration and Citizenship Agency</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8700,6 +10517,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Passport, Immigration and Citizenship Agency Budget 1 - Recurrent</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8745,6 +10577,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8790,6 +10632,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8835,6 +10687,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8880,6 +10742,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8894,7 +10766,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Ministry of Justice" --&gt;</t>
+          <t>Ministry of Justice</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8915,6 +10787,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Ministry of Justice" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8960,6 +10839,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9005,6 +10894,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9019,7 +10918,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Ministry of Justice" --&gt;</t>
+          <t>Ministry of Justice</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9050,6 +10949,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Ministry of Justice" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9085,6 +10999,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9130,6 +11046,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9175,6 +11101,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9220,6 +11156,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9265,6 +11211,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9310,6 +11266,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9345,6 +11311,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9390,6 +11358,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9435,6 +11413,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9480,6 +11468,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9515,6 +11513,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9560,6 +11560,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9605,6 +11615,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9619,7 +11639,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Minstry of Health and Wellness" --&gt;</t>
+          <t>Ministry of Health and Wellness</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9640,6 +11660,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Minstry of Health and Wellness" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9685,6 +11712,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9730,6 +11767,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9775,6 +11822,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9820,6 +11877,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9834,7 +11901,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Minstry of Health and Wellness" --&gt;</t>
+          <t>Ministry of Health and Wellness</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9865,6 +11932,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Minstry of Health and Wellness" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9910,6 +11992,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9955,6 +12047,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10000,6 +12102,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10045,6 +12157,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10059,7 +12181,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Ministry of Culture, Gender, Entertainment and Sport" --&gt;</t>
+          <t>Ministry of Culture, Gender, Entertainment and Sport</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10080,6 +12202,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Ministry of Culture, Gender, Entertainment and Sport" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10125,6 +12254,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10170,6 +12309,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10215,6 +12364,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10260,6 +12419,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10305,6 +12474,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10350,6 +12529,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10364,7 +12553,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture and Fisheries" --&gt;</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -10385,6 +12574,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and Fisheries" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10430,6 +12626,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10475,6 +12681,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10489,7 +12705,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture and Fisheries" --&gt;</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -10520,6 +12736,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture and Fisheries" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10534,7 +12765,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+          <t>Ministry of Industry, Investment and Commerce</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10555,6 +12786,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10600,6 +12838,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10645,6 +12893,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10659,7 +12917,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+          <t>Ministry of Industry, Investment and Commerce</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10690,6 +12948,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10725,6 +12998,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10770,6 +13045,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10815,6 +13100,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10829,7 +13124,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology" --&gt;</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -10850,6 +13145,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10864,7 +13166,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10895,6 +13197,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10909,7 +13226,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10940,6 +13257,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10954,7 +13286,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10985,6 +13317,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10999,7 +13346,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11030,6 +13377,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11044,7 +13406,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11075,6 +13437,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11089,7 +13466,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy and Technology" --&gt;</t>
+          <t>Ministry of Science and Technology" --&gt;</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11120,6 +13497,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy and Technology" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11155,6 +13547,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11200,6 +13594,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11214,7 +13618,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Ministry of Local Government and Rural Development</t>
+          <t>Ministry of Local Government and Community</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11245,6 +13649,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2022.xlsx</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Ministry of Local Government and Rural Development</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11280,6 +13699,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11325,6 +13746,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11370,6 +13801,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11415,6 +13856,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11450,6 +13901,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11495,6 +13948,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11540,6 +14003,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11585,6 +14058,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11630,6 +14113,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11675,6 +14168,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11720,6 +14223,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11765,6 +14278,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11800,6 +14323,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11845,6 +14370,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11890,6 +14425,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11935,6 +14480,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11980,6 +14535,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12025,6 +14590,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12070,6 +14645,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12115,6 +14700,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12160,6 +14755,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12174,7 +14779,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Registrar General's Department and Island Records Office</t>
+          <t>Registrar General's Department and Island Records</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -12195,6 +14800,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Registrar General's Department and Island Records Office</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12240,6 +14852,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12285,6 +14907,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12320,6 +14952,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12365,6 +14999,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12410,6 +15054,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12455,6 +15109,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12500,6 +15164,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12535,6 +15209,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12580,6 +15256,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -12625,6 +15311,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -12660,6 +15356,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -12674,7 +15372,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Ministry of Economic Growth and Job Creation</t>
+          <t>Ministry of Economic Growth and Job Creation" --&gt;</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -12705,6 +15403,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Growth and Job Creation</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -12719,7 +15432,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Ministry of Economic Growth and Job Creation</t>
+          <t>Ministry of Economic Growth and Job Creation" --&gt;</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -12750,6 +15463,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Growth and Job Creation</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -12764,7 +15492,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Ministry of Economic Growth and Job Creation</t>
+          <t>Ministry of Economic Growth and Job Creation" --&gt;</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -12795,6 +15523,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Growth and Job Creation</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12809,7 +15552,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Ministry of Economic Growth and Job Creation</t>
+          <t>Ministry of Economic Growth and Job Creation" --&gt;</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -12840,6 +15583,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Growth and Job Creation</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12854,7 +15612,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Ministry of Economic Growth and Job Creation</t>
+          <t>Ministry of Economic Growth and Job Creation" --&gt;</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -12885,6 +15643,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Growth and Job Creation</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12899,7 +15672,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Ministry of Economic Growth and Job Creation</t>
+          <t>Ministry of Economic Growth and Job Creation" --&gt;</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -12930,6 +15703,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Growth and Job Creation</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12975,6 +15763,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13020,6 +15818,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13065,6 +15873,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13110,6 +15928,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13155,6 +15983,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13200,6 +16038,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -13235,6 +16083,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13280,6 +16130,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13325,6 +16185,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13360,6 +16230,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13405,6 +16277,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13450,6 +16332,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -13495,6 +16387,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13530,6 +16432,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -13575,6 +16479,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -13620,6 +16534,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -13655,6 +16579,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -13669,7 +16595,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -13700,6 +16626,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -13714,7 +16655,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -13745,6 +16686,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13759,7 +16715,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -13790,6 +16746,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -13804,7 +16775,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -13835,6 +16806,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -13849,7 +16835,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -13880,6 +16866,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13894,7 +16895,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -13925,6 +16926,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13939,7 +16955,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Ministry of Finance and the Public Service</t>
+          <t>Ministry of Finance and The Public Service" --&gt;</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -13970,6 +16986,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Ministry of Finance and the Public Service</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14015,6 +17046,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14060,6 +17101,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14105,6 +17156,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14150,6 +17211,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14195,6 +17266,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14240,6 +17321,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14285,6 +17376,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14330,6 +17431,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14375,6 +17486,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14410,6 +17531,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -14455,6 +17578,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14500,6 +17633,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -14514,7 +17657,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -14535,6 +17678,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -14580,6 +17730,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -14625,6 +17785,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -14670,6 +17840,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -14684,7 +17864,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -14715,6 +17895,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -14729,7 +17924,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Ministry of National Security" --&gt;</t>
+          <t>Ministry of National Security</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -14760,6 +17955,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Ministry of National Security" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -14795,6 +18005,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -14840,6 +18052,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -14885,6 +18107,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -14930,6 +18162,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -14975,6 +18217,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15010,6 +18262,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15055,6 +18309,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15100,6 +18364,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -15135,6 +18409,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15180,6 +18456,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -15194,7 +18480,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Ministry of Justice" --&gt;</t>
+          <t>Ministry of Justice</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -15215,6 +18501,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Ministry of Justice" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15260,6 +18553,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -15305,6 +18608,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -15319,7 +18632,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Ministry of Justice" --&gt;</t>
+          <t>Ministry of Justice</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -15350,6 +18663,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Ministry of Justice" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -15385,6 +18713,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -15430,6 +18760,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -15475,6 +18815,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -15520,6 +18870,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -15565,6 +18925,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -15610,6 +18980,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -15655,6 +19035,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -15690,6 +19080,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -15735,6 +19127,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -15780,6 +19182,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -15825,6 +19237,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -15870,6 +19292,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -15915,6 +19347,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -15960,6 +19402,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16005,6 +19457,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16050,6 +19512,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16095,6 +19567,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16140,6 +19622,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -16154,7 +19646,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Ministry of Education and Youth" --&gt;</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -16185,6 +19677,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Ministry of Education and Youth" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16199,7 +19706,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Ministry of Education and Youth" --&gt;</t>
+          <t>Ministry of Education and Youth Budget 1 - Recurrent Function 09 - Education Affairs and Services SubFunction 07 - Subsidiary Services to Education Programme 261 - Education and Training Services" --&gt;</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -16230,6 +19737,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Ministry of Education and Youth" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -16265,6 +19787,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16279,7 +19803,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Child Protection and Family Services Agency Budget 1 - Recurrent</t>
+          <t>Child Protection and Family Services Agency</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -16310,6 +19834,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Child Protection and Family Services Agency Budget 1 - Recurrent</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16324,7 +19863,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Child Protection and Family Services Agency Budget 1 - Recurrent</t>
+          <t>Child Protection and Family Services Agency</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -16355,6 +19894,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Child Protection and Family Services Agency Budget 1 - Recurrent</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16369,7 +19923,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Ministry of Health and Wellness" --&gt;</t>
+          <t>Ministry of Health and Wellness</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -16390,6 +19944,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Ministry of Health and Wellness" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16435,6 +19996,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -16480,6 +20051,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -16525,6 +20106,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -16570,6 +20161,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -16584,7 +20185,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Ministry of Health and Wellness" --&gt;</t>
+          <t>Ministry of Health and Wellness</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -16615,6 +20216,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Ministry of Health and Wellness" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -16650,6 +20266,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -16695,6 +20313,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -16740,6 +20368,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -16785,6 +20423,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -16830,6 +20478,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -16875,6 +20533,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -16920,6 +20588,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -16934,7 +20612,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture, Fisheries and Mining" --&gt;</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -16955,6 +20633,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Fisheries and Mining" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -16969,7 +20654,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture, Fisheries and Mining</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -17000,6 +20685,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Fisheries and Mining</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -17014,7 +20714,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture, Fisheries and Mining</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -17045,6 +20745,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Fisheries and Mining</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -17059,7 +20774,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture, Fisheries and Mining</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -17090,6 +20805,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Fisheries and Mining</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -17104,7 +20834,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture, Fisheries and Mining</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -17135,6 +20865,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Fisheries and Mining</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -17149,7 +20894,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture, Fisheries and Mining" --&gt;</t>
+          <t>Ministry of Agriculture and Fisheries</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -17180,6 +20925,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Fisheries and Mining" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -17194,7 +20954,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+          <t>Ministry of Industry, Investment and Commerce</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -17215,6 +20975,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -17260,6 +21027,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -17305,6 +21082,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -17350,6 +21137,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -17395,6 +21192,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17409,7 +21216,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+          <t>Ministry of Industry, Investment and Commerce</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -17440,6 +21247,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -17475,6 +21297,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17520,6 +21344,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -17565,6 +21399,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -17600,6 +21444,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17614,7 +21460,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -17645,6 +21491,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -17659,7 +21520,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -17690,6 +21551,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -17704,7 +21580,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -17735,6 +21611,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -17749,7 +21640,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -17780,6 +21671,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -17794,7 +21700,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -17825,6 +21731,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -17839,7 +21760,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -17870,6 +21791,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -17884,7 +21820,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -17915,6 +21851,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -17929,7 +21880,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -17960,6 +21911,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -17974,7 +21940,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Ministry of Science, Energy, Telecommunications and</t>
+          <t>Ministry of Science, Energy Telecommunications and Transport" --&gt;</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -18005,6 +21971,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Ministry of Science, Energy, Telecommunications and</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -18050,6 +22031,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -18095,6 +22086,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -18109,7 +22110,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Ministry of Local Government and Community Development" --&gt;</t>
+          <t>Ministry of Local Government and Community</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -18130,6 +22131,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Ministry of Local Government and Community Development" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -18175,6 +22183,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -18220,6 +22238,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -18265,6 +22293,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18310,6 +22348,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -18355,6 +22403,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -18400,6 +22458,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -18445,6 +22513,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -18490,6 +22568,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18504,7 +22592,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Ministry of Local Government and Community Development" --&gt;</t>
+          <t>Ministry of Local Government and Community</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -18535,6 +22623,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Ministry of Local Government and Community Development" --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -18549,7 +22652,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Ministry of Local Government and Community Development" --&gt;</t>
+          <t>Ministry of Local Government and Community</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -18578,6 +22681,21 @@
       <c r="J421" t="inlineStr">
         <is>
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/jamaica/jamaica_budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Ministry of Local Government and Community Development" --&gt;</t>
         </is>
       </c>
     </row>

--- a/jamaica/budget_layer_all_years.xlsx
+++ b/jamaica/budget_layer_all_years.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="budget_all_years" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programs_wide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="national_total" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27707,7 +27708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27718,27 +27719,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>head_total</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>strategy_total</t>
+          <t>programme_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>program_sum</t>
+          <t>gap_pct</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>basis</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>nested_heads</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>national</t>
         </is>
       </c>
     </row>
@@ -27748,2052 +27754,79 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
+      <c r="B2" t="n">
+        <v>278267320</v>
       </c>
       <c r="C2" t="n">
-        <v>290111</v>
+        <v>239480965</v>
       </c>
       <c r="D2" t="n">
-        <v>83000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>207111</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
+        <v>13.94</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>programmes</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>239480965</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>08000</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>302576866</v>
       </c>
       <c r="C3" t="n">
-        <v>469975</v>
+        <v>404258046</v>
       </c>
       <c r="D3" t="n">
-        <v>642858</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-172883</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
+        <v>25.15</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>programmes</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>404258046</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>09000</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>458257529</v>
       </c>
       <c r="C4" t="n">
-        <v>833920</v>
+        <v>639705043</v>
       </c>
       <c r="D4" t="n">
-        <v>712147</v>
-      </c>
-      <c r="E4" t="n">
-        <v>121773</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>7952226</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7952226</v>
-      </c>
-      <c r="E5" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>programmes</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>697424</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>697424</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>15020</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>10480</v>
-      </c>
-      <c r="D7" t="n">
-        <v>900480</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-890000</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>16049</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>225234</v>
-      </c>
-      <c r="D8" t="n">
-        <v>489234</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-264000</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>17000</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>11525361</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6345325</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5180036</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>19000</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>18424497</v>
-      </c>
-      <c r="D10" t="n">
-        <v>18424497</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>19046</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1078318</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1085718</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-7400</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20056</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>10054843</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10054843</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>26000</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>44836807</v>
-      </c>
-      <c r="D13" t="n">
-        <v>45308512</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-471705</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>26022</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>39423260</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>39423260</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>26024</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>7611526</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7621526</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>26053</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>28811</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>28811</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2061385</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3866946</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1805561</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>28030</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>317177</v>
-      </c>
-      <c r="D18" t="n">
-        <v>542177</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-225000</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4811749</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4811749</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>41000</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>106723489</v>
-      </c>
-      <c r="D20" t="n">
-        <v>107548489</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-825000</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>9597784</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9597784</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>50038</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>14019</v>
-      </c>
-      <c r="D22" t="n">
-        <v>483604</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-469585</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>35872</v>
-      </c>
-      <c r="D23" t="n">
-        <v>35872</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>72000</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>11243052</v>
-      </c>
-      <c r="D24" t="n">
-        <v>423040</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10820012</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>407675</v>
-      </c>
-      <c r="D25" t="n">
-        <v>95774</v>
-      </c>
-      <c r="E25" t="n">
-        <v>311901</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>05000</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1087007</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1080720</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6287</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>08000</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>612308</v>
-      </c>
-      <c r="D27" t="n">
-        <v>763809</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-151501</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09000</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1150532</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1115532</v>
-      </c>
-      <c r="E28" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>4507458</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4507458</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>680846</v>
-      </c>
-      <c r="D30" t="n">
-        <v>798913</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-118067</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>15020</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>659370</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1317383</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-658013</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>16049</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>274923</v>
-      </c>
-      <c r="D32" t="n">
-        <v>497725</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-222802</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>17000</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>11507204</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>11507204</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>19000</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>8927891</v>
-      </c>
-      <c r="D34" t="n">
-        <v>29765294</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-20837403</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>19046</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1090013</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1100013</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>19047</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>858517</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3679751</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-2821234</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>19050</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>873915</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2268474</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-1394559</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>49576488</v>
-      </c>
-      <c r="D38" t="n">
-        <v>58653448</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-9076960</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>26000</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>34248397</v>
-      </c>
-      <c r="D39" t="n">
-        <v>42338420</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-8090023</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>26022</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>46117077</v>
-      </c>
-      <c r="D40" t="n">
-        <v>46517077</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>26024</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>8903647</v>
-      </c>
-      <c r="D41" t="n">
-        <v>7948845</v>
-      </c>
-      <c r="E41" t="n">
-        <v>954802</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>26053</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1121806</v>
-      </c>
-      <c r="D42" t="n">
-        <v>4002887</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-2881081</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2567834</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2838834</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-271000</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>28030</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>397438</v>
-      </c>
-      <c r="D44" t="n">
-        <v>662438</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-265000</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5030141</v>
-      </c>
-      <c r="D45" t="n">
-        <v>5173346</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-143205</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>41051</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>3136230</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3138093</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-1863</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>42000</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>91011996</v>
-      </c>
-      <c r="D47" t="n">
-        <v>96361130</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-5349134</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>46000</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>4407217</v>
-      </c>
-      <c r="D48" t="n">
-        <v>4680006</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-272789</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>51000</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>10224964</v>
-      </c>
-      <c r="D49" t="n">
-        <v>16159097</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-5934133</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>53000</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>4290996</v>
-      </c>
-      <c r="D50" t="n">
-        <v>4283155</v>
-      </c>
-      <c r="E50" t="n">
-        <v>7841</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>53038</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>8860</v>
-      </c>
-      <c r="D51" t="n">
-        <v>711596</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-702736</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>6480924</v>
-      </c>
-      <c r="D52" t="n">
-        <v>7722180</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-1241256</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>56039</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2415192</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2319020</v>
-      </c>
-      <c r="E53" t="n">
-        <v>96172</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>532852</v>
-      </c>
-      <c r="D54" t="n">
-        <v>153972</v>
-      </c>
-      <c r="E54" t="n">
-        <v>378880</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>05000</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1404352</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1385839</v>
-      </c>
-      <c r="E55" t="n">
-        <v>18513</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>08000</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>837299</v>
-      </c>
-      <c r="D56" t="n">
-        <v>885134</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-47835</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>15020</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>516078</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1462358</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-946280</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>15039</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>3502373</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4252373</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-750000</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>16049</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>274923</v>
-      </c>
-      <c r="D59" t="n">
-        <v>574923</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-300000</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>19000</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>12439289</v>
-      </c>
-      <c r="D60" t="n">
-        <v>34051450</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-21612161</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>19046</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1731204</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1766204</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-35000</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>19047</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1568816</v>
-      </c>
-      <c r="D62" t="n">
-        <v>5008264</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-3439448</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>19050</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1288476</v>
-      </c>
-      <c r="D63" t="n">
-        <v>3090257</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-1801781</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>90947481</v>
-      </c>
-      <c r="D64" t="n">
-        <v>117307933</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-26360452</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>20060</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1461711</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1561711</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>26000</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>47390535</v>
-      </c>
-      <c r="D66" t="n">
-        <v>51798405</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-4407870</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>26022</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>69973343</v>
-      </c>
-      <c r="D67" t="n">
-        <v>70423343</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-450000</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>26053</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1032106</v>
-      </c>
-      <c r="D68" t="n">
-        <v>5080641</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-4048535</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>26059</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>2886099</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1033661</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1852438</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>3690999</v>
-      </c>
-      <c r="D70" t="n">
-        <v>4275364</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-584365</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>28030</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>438367</v>
-      </c>
-      <c r="D71" t="n">
-        <v>885108</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-446741</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>6651435</v>
-      </c>
-      <c r="D72" t="n">
-        <v>6751435</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>41051</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>4756586</v>
-      </c>
-      <c r="D73" t="n">
-        <v>4758206</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-1620</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>42000</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>133605851</v>
-      </c>
-      <c r="D74" t="n">
-        <v>145655364</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-12049513</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>46000</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>5856463</v>
-      </c>
-      <c r="D75" t="n">
-        <v>6205640</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-349177</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>51000</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>14084411</v>
-      </c>
-      <c r="D76" t="n">
-        <v>19608348</v>
-      </c>
-      <c r="E76" t="n">
-        <v>-5523937</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>53000</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>6134940</v>
-      </c>
-      <c r="D77" t="n">
-        <v>6974892</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-839952</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>53038</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>679042</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1245569</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-566527</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>69000</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>23793602</v>
-      </c>
-      <c r="D79" t="n">
-        <v>27873661</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-4080059</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>72000</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>20778896</v>
-      </c>
-      <c r="D80" t="n">
-        <v>26555683</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-5776787</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
+      <c r="G4" t="n">
+        <v>639705043</v>
       </c>
     </row>
   </sheetData>
@@ -29807,50 +27840,2150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F280"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>fiscal_year</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>strategy_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>fiscal_year</t>
+          <t>strategy_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>program_sum</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>program_code</t>
+          <t>diff</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>290111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>83000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>207111</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>08000</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>469975</v>
+      </c>
+      <c r="D3" t="n">
+        <v>642858</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-172883</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>09000</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>833920</v>
+      </c>
+      <c r="D4" t="n">
+        <v>712147</v>
+      </c>
+      <c r="E4" t="n">
+        <v>121773</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7952226</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7952226</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>697424</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>697424</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15020</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10480</v>
+      </c>
+      <c r="D7" t="n">
+        <v>900480</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-890000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16049</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>225234</v>
+      </c>
+      <c r="D8" t="n">
+        <v>489234</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-264000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11525361</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6345325</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5180036</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>18424497</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18424497</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19046</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1078318</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1085718</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-7400</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20056</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10054843</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10054843</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>44836807</v>
+      </c>
+      <c r="D13" t="n">
+        <v>45308512</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-471705</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>26022</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>39423260</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39423260</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26024</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7611526</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7621526</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>26053</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>28811</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>28811</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2061385</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3866946</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1805561</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>28030</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>317177</v>
+      </c>
+      <c r="D18" t="n">
+        <v>542177</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4811749</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4811749</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>41000</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>106723489</v>
+      </c>
+      <c r="D20" t="n">
+        <v>107548489</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-825000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9597784</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9597784</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>50038</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>14019</v>
+      </c>
+      <c r="D22" t="n">
+        <v>483604</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-469585</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>56000</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35872</v>
+      </c>
+      <c r="D23" t="n">
+        <v>35872</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11243052</v>
+      </c>
+      <c r="D24" t="n">
+        <v>423040</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10820012</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>407675</v>
+      </c>
+      <c r="D25" t="n">
+        <v>95774</v>
+      </c>
+      <c r="E25" t="n">
+        <v>311901</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>05000</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1087007</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1080720</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6287</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08000</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>612308</v>
+      </c>
+      <c r="D27" t="n">
+        <v>763809</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-151501</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09000</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1150532</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1115532</v>
+      </c>
+      <c r="E28" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4507458</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4507458</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>15010</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>680846</v>
+      </c>
+      <c r="D30" t="n">
+        <v>798913</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-118067</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>15020</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>659370</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1317383</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-658013</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16049</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>274923</v>
+      </c>
+      <c r="D32" t="n">
+        <v>497725</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-222802</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>11507204</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11507204</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>8927891</v>
+      </c>
+      <c r="D34" t="n">
+        <v>29765294</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-20837403</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>19046</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1090013</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>19047</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>858517</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3679751</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2821234</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>19050</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>873915</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2268474</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1394559</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>49576488</v>
+      </c>
+      <c r="D38" t="n">
+        <v>58653448</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-9076960</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>34248397</v>
+      </c>
+      <c r="D39" t="n">
+        <v>42338420</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-8090023</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>26022</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>46117077</v>
+      </c>
+      <c r="D40" t="n">
+        <v>46517077</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>26024</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8903647</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7948845</v>
+      </c>
+      <c r="E41" t="n">
+        <v>954802</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>26053</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1121806</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4002887</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-2881081</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2567834</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2838834</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-271000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>28030</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>397438</v>
+      </c>
+      <c r="D44" t="n">
+        <v>662438</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-265000</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5030141</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5173346</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-143205</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>41051</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3136230</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3138093</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1863</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>91011996</v>
+      </c>
+      <c r="D47" t="n">
+        <v>96361130</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-5349134</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4407217</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4680006</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-272789</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>51000</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10224964</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16159097</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-5934133</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>53000</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4290996</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4283155</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7841</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>53038</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8860</v>
+      </c>
+      <c r="D51" t="n">
+        <v>711596</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-702736</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>56000</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6480924</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7722180</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-1241256</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>56039</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2415192</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2319020</v>
+      </c>
+      <c r="E53" t="n">
+        <v>96172</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>01000</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>532852</v>
+      </c>
+      <c r="D54" t="n">
+        <v>153972</v>
+      </c>
+      <c r="E54" t="n">
+        <v>378880</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>05000</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1404352</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1385839</v>
+      </c>
+      <c r="E55" t="n">
+        <v>18513</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>08000</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>837299</v>
+      </c>
+      <c r="D56" t="n">
+        <v>885134</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-47835</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>15020</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>516078</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1462358</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-946280</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>15039</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3502373</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4252373</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-750000</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>16049</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>274923</v>
+      </c>
+      <c r="D59" t="n">
+        <v>574923</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>19000</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>12439289</v>
+      </c>
+      <c r="D60" t="n">
+        <v>34051450</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-21612161</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>19046</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1731204</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1766204</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>19047</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1568816</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5008264</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-3439448</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>19050</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1288476</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3090257</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-1801781</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>90947481</v>
+      </c>
+      <c r="D64" t="n">
+        <v>117307933</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-26360452</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20060</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1461711</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1561711</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>47390535</v>
+      </c>
+      <c r="D66" t="n">
+        <v>51798405</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-4407870</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>26022</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>69973343</v>
+      </c>
+      <c r="D67" t="n">
+        <v>70423343</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-450000</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>26053</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1032106</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5080641</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-4048535</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>26059</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2886099</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1033661</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1852438</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>3690999</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4275364</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-584365</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>28030</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>438367</v>
+      </c>
+      <c r="D71" t="n">
+        <v>885108</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-446741</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6651435</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6751435</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>41051</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4756586</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4758206</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-1620</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>133605851</v>
+      </c>
+      <c r="D74" t="n">
+        <v>145655364</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-12049513</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5856463</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6205640</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-349177</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>51000</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>14084411</v>
+      </c>
+      <c r="D76" t="n">
+        <v>19608348</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-5523937</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>53000</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6134940</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6974892</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-839952</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>53038</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>679042</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1245569</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-566527</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>23793602</v>
+      </c>
+      <c r="D79" t="n">
+        <v>27873661</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-4080059</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>20778896</v>
+      </c>
+      <c r="D80" t="n">
+        <v>26555683</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-5776787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F283"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>strategy_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>program_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reconciliation_mismatch</t>
+          <t>national_basis_programmes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -29858,15 +29991,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>01000</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>programs sum to 83,000.0 but strategy_total is 290,111.0 (gap 207,111.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>head totals sum to 278,267,320.0 but the programmes beneath them sum to 239,480,965.0 (14% apart), so the national total for this year is taken from the PROGRAMME rows. Every share for FY2019 is computed against 239,480,965.0.</t>
         </is>
       </c>
     </row>
@@ -29878,23 +30007,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>reconciliation_mismatch</t>
+          <t>national_basis_programmes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>08000</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>programs sum to 642,858.0 but strategy_total is 469,975.0 (gap -172,883.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>head totals sum to 302,576,866.0 but the programmes beneath them sum to 404,258,046.0 (25% apart), so the national total for this year is taken from the PROGRAMME rows. Every share for FY2022 is computed against 404,258,046.0.</t>
         </is>
       </c>
     </row>
@@ -29906,23 +30031,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reconciliation_mismatch</t>
+          <t>national_basis_programmes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>09000</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>programs sum to 712,147.0 but strategy_total is 833,920.0 (gap 121,773.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>head totals sum to 458,257,529.0 but the programmes beneath them sum to 639,705,043.0 (28% apart), so the national total for this year is taken from the PROGRAMME rows. Every share for FY2024 is computed against 639,705,043.0.</t>
         </is>
       </c>
     </row>
@@ -29944,13 +30065,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>01000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 697,424.0 (gap 697,424.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 83,000.0 but strategy_total is 290,111.0 (gap 207,111.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -29972,13 +30093,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>08000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>programs sum to 900,480.0 but strategy_total is 10,480.0 (gap -890,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 642,858.0 but strategy_total is 469,975.0 (gap -172,883.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30000,13 +30121,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>09000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>programs sum to 489,234.0 but strategy_total is 225,234.0 (gap -264,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 712,147.0 but strategy_total is 833,920.0 (gap 121,773.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30028,13 +30149,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>programs sum to 6,345,325.0 but strategy_total is 11,525,361.0 (gap 5,180,036.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 697,424.0 (gap 697,424.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30056,13 +30177,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>programs sum to 1,085,718.0 but strategy_total is 1,078,318.0 (gap -7,400.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 900,480.0 but strategy_total is 10,480.0 (gap -890,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30084,13 +30205,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>programs sum to 45,308,512.0 but strategy_total is 44,836,807.0 (gap -471,705.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 489,234.0 but strategy_total is 225,234.0 (gap -264,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30112,13 +30233,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 39,423,260.0 (gap 39,423,260.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 6,345,325.0 but strategy_total is 11,525,361.0 (gap 5,180,036.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30140,13 +30261,13 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>programs sum to 7,621,526.0 but strategy_total is 7,611,526.0 (gap -10,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,085,718.0 but strategy_total is 1,078,318.0 (gap -7,400.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30168,13 +30289,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 28,811.0 (gap 28,811.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 45,308,512.0 but strategy_total is 44,836,807.0 (gap -471,705.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30196,13 +30317,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>programs sum to 3,866,946.0 but strategy_total is 2,061,385.0 (gap -1,805,561.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 39,423,260.0 (gap 39,423,260.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30224,13 +30345,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>programs sum to 542,177.0 but strategy_total is 317,177.0 (gap -225,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 7,621,526.0 but strategy_total is 7,611,526.0 (gap -10,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30252,13 +30373,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 4,811,749.0 (gap 4,811,749.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 28,811.0 (gap 28,811.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30280,13 +30401,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>programs sum to 107,548,489.0 but strategy_total is 106,723,489.0 (gap -825,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 3,866,946.0 but strategy_total is 2,061,385.0 (gap -1,805,561.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30308,13 +30429,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 9,597,784.0 (gap 9,597,784.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 542,177.0 but strategy_total is 317,177.0 (gap -225,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30336,13 +30457,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>programs sum to 483,604.0 but strategy_total is 14,019.0 (gap -469,585.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 4,811,749.0 (gap 4,811,749.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30364,13 +30485,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>programs sum to 423,040.0 but strategy_total is 11,243,052.0 (gap 10,820,012.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 107,548,489.0 but strategy_total is 106,723,489.0 (gap -825,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30387,18 +30508,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>programs sum to 95,774.0 but strategy_total is 407,675.0 (gap 311,901.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 9,597,784.0 (gap 9,597,784.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30415,18 +30536,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05000</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>programs sum to 1,080,720.0 but strategy_total is 1,087,007.0 (gap 6,287.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 483,604.0 but strategy_total is 14,019.0 (gap -469,585.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30443,18 +30564,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>programs sum to 763,809.0 but strategy_total is 612,308.0 (gap -151,501.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 423,040.0 but strategy_total is 11,243,052.0 (gap 10,820,012.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30476,13 +30597,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>09000</t>
+          <t>01000</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>programs sum to 1,115,532.0 but strategy_total is 1,150,532.0 (gap 35,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 95,774.0 but strategy_total is 407,675.0 (gap 311,901.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30504,13 +30625,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>programs sum to 798,913.0 but strategy_total is 680,846.0 (gap -118,067.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,080,720.0 but strategy_total is 1,087,007.0 (gap 6,287.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30532,13 +30653,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>08000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>programs sum to 1,317,383.0 but strategy_total is 659,370.0 (gap -658,013.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 763,809.0 but strategy_total is 612,308.0 (gap -151,501.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30560,13 +30681,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>09000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>programs sum to 497,725.0 but strategy_total is 274,923.0 (gap -222,802.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,115,532.0 but strategy_total is 1,150,532.0 (gap 35,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30588,13 +30709,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 11,507,204.0 (gap 11,507,204.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 798,913.0 but strategy_total is 680,846.0 (gap -118,067.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30616,13 +30737,13 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>programs sum to 29,765,294.0 but strategy_total is 8,927,891.0 (gap -20,837,403.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,317,383.0 but strategy_total is 659,370.0 (gap -658,013.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30644,13 +30765,13 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>programs sum to 1,100,013.0 but strategy_total is 1,090,013.0 (gap -10,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 497,725.0 but strategy_total is 274,923.0 (gap -222,802.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30672,13 +30793,13 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>programs sum to 3,679,751.0 but strategy_total is 858,517.0 (gap -2,821,234.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 11,507,204.0 (gap 11,507,204.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30700,13 +30821,13 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>programs sum to 2,268,474.0 but strategy_total is 873,915.0 (gap -1,394,559.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 29,765,294.0 but strategy_total is 8,927,891.0 (gap -20,837,403.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30728,13 +30849,13 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>programs sum to 58,653,448.0 but strategy_total is 49,576,488.0 (gap -9,076,960.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,100,013.0 but strategy_total is 1,090,013.0 (gap -10,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30756,13 +30877,13 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>programs sum to 42,338,420.0 but strategy_total is 34,248,397.0 (gap -8,090,023.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 3,679,751.0 but strategy_total is 858,517.0 (gap -2,821,234.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30784,13 +30905,13 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>programs sum to 46,517,077.0 but strategy_total is 46,117,077.0 (gap -400,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 2,268,474.0 but strategy_total is 873,915.0 (gap -1,394,559.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30812,13 +30933,13 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>programs sum to 7,948,845.0 but strategy_total is 8,903,647.0 (gap 954,802.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 58,653,448.0 but strategy_total is 49,576,488.0 (gap -9,076,960.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30840,13 +30961,13 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>programs sum to 4,002,887.0 but strategy_total is 1,121,806.0 (gap -2,881,081.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 42,338,420.0 but strategy_total is 34,248,397.0 (gap -8,090,023.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30868,13 +30989,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>programs sum to 2,838,834.0 but strategy_total is 2,567,834.0 (gap -271,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 46,517,077.0 but strategy_total is 46,117,077.0 (gap -400,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30896,13 +31017,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>programs sum to 662,438.0 but strategy_total is 397,438.0 (gap -265,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 7,948,845.0 but strategy_total is 8,903,647.0 (gap 954,802.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30924,13 +31045,13 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>programs sum to 5,173,346.0 but strategy_total is 5,030,141.0 (gap -143,205.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 4,002,887.0 but strategy_total is 1,121,806.0 (gap -2,881,081.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30952,13 +31073,13 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>programs sum to 3,138,093.0 but strategy_total is 3,136,230.0 (gap -1,863.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 2,838,834.0 but strategy_total is 2,567,834.0 (gap -271,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -30980,13 +31101,13 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>programs sum to 96,361,130.0 but strategy_total is 91,011,996.0 (gap -5,349,134.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 662,438.0 but strategy_total is 397,438.0 (gap -265,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31008,13 +31129,13 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>programs sum to 4,680,006.0 but strategy_total is 4,407,217.0 (gap -272,789.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 5,173,346.0 but strategy_total is 5,030,141.0 (gap -143,205.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31036,13 +31157,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>programs sum to 16,159,097.0 but strategy_total is 10,224,964.0 (gap -5,934,133.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 3,138,093.0 but strategy_total is 3,136,230.0 (gap -1,863.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31064,13 +31185,13 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>programs sum to 4,283,155.0 but strategy_total is 4,290,996.0 (gap 7,841.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 96,361,130.0 but strategy_total is 91,011,996.0 (gap -5,349,134.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31092,13 +31213,13 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>programs sum to 711,596.0 but strategy_total is 8,860.0 (gap -702,736.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 4,680,006.0 but strategy_total is 4,407,217.0 (gap -272,789.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31120,13 +31241,13 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>programs sum to 7,722,180.0 but strategy_total is 6,480,924.0 (gap -1,241,256.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 16,159,097.0 but strategy_total is 10,224,964.0 (gap -5,934,133.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31148,13 +31269,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>programs sum to 2,319,020.0 but strategy_total is 2,415,192.0 (gap 96,172.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 4,283,155.0 but strategy_total is 4,290,996.0 (gap 7,841.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31171,18 +31292,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>01000</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>programs sum to 153,972.0 but strategy_total is 532,852.0 (gap 378,880.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 711,596.0 but strategy_total is 8,860.0 (gap -702,736.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31199,18 +31320,18 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>05000</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>programs sum to 1,385,839.0 but strategy_total is 1,404,352.0 (gap 18,513.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 7,722,180.0 but strategy_total is 6,480,924.0 (gap -1,241,256.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31227,18 +31348,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08000</t>
+          <t>56039</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>programs sum to 885,134.0 but strategy_total is 837,299.0 (gap -47,835.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 2,319,020.0 but strategy_total is 2,415,192.0 (gap 96,172.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31260,13 +31381,13 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>01000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>programs sum to 1,462,358.0 but strategy_total is 516,078.0 (gap -946,280.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 153,972.0 but strategy_total is 532,852.0 (gap 378,880.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31288,13 +31409,13 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>programs sum to 4,252,373.0 but strategy_total is 3,502,373.0 (gap -750,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,385,839.0 but strategy_total is 1,404,352.0 (gap 18,513.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31316,13 +31437,13 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>08000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>programs sum to 574,923.0 but strategy_total is 274,923.0 (gap -300,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 885,134.0 but strategy_total is 837,299.0 (gap -47,835.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31344,13 +31465,13 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>programs sum to 34,051,450.0 but strategy_total is 12,439,289.0 (gap -21,612,161.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,462,358.0 but strategy_total is 516,078.0 (gap -946,280.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31372,13 +31493,13 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>programs sum to 1,766,204.0 but strategy_total is 1,731,204.0 (gap -35,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 4,252,373.0 but strategy_total is 3,502,373.0 (gap -750,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31400,13 +31521,13 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>programs sum to 5,008,264.0 but strategy_total is 1,568,816.0 (gap -3,439,448.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 574,923.0 but strategy_total is 274,923.0 (gap -300,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31428,13 +31549,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>programs sum to 3,090,257.0 but strategy_total is 1,288,476.0 (gap -1,801,781.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 34,051,450.0 but strategy_total is 12,439,289.0 (gap -21,612,161.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31456,13 +31577,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>programs sum to 117,307,933.0 but strategy_total is 90,947,481.0 (gap -26,360,452.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,766,204.0 but strategy_total is 1,731,204.0 (gap -35,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31484,13 +31605,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>programs sum to 1,561,711.0 but strategy_total is 1,461,711.0 (gap -100,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 5,008,264.0 but strategy_total is 1,568,816.0 (gap -3,439,448.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31512,13 +31633,13 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>programs sum to 51,798,405.0 but strategy_total is 47,390,535.0 (gap -4,407,870.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 3,090,257.0 but strategy_total is 1,288,476.0 (gap -1,801,781.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31540,13 +31661,13 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>programs sum to 70,423,343.0 but strategy_total is 69,973,343.0 (gap -450,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 117,307,933.0 but strategy_total is 90,947,481.0 (gap -26,360,452.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31568,13 +31689,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>programs sum to 5,080,641.0 but strategy_total is 1,032,106.0 (gap -4,048,535.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,561,711.0 but strategy_total is 1,461,711.0 (gap -100,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31596,13 +31717,13 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>programs sum to 1,033,661.0 but strategy_total is 2,886,099.0 (gap 1,852,438.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 51,798,405.0 but strategy_total is 47,390,535.0 (gap -4,407,870.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31624,13 +31745,13 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>programs sum to 4,275,364.0 but strategy_total is 3,690,999.0 (gap -584,365.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 70,423,343.0 but strategy_total is 69,973,343.0 (gap -450,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31652,13 +31773,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>programs sum to 885,108.0 but strategy_total is 438,367.0 (gap -446,741.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 5,080,641.0 but strategy_total is 1,032,106.0 (gap -4,048,535.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31680,13 +31801,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>programs sum to 6,751,435.0 but strategy_total is 6,651,435.0 (gap -100,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 1,033,661.0 but strategy_total is 2,886,099.0 (gap 1,852,438.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31708,13 +31829,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>programs sum to 4,758,206.0 but strategy_total is 4,756,586.0 (gap -1,620.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 4,275,364.0 but strategy_total is 3,690,999.0 (gap -584,365.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31736,13 +31857,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>programs sum to 145,655,364.0 but strategy_total is 133,605,851.0 (gap -12,049,513.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 885,108.0 but strategy_total is 438,367.0 (gap -446,741.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31764,13 +31885,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>programs sum to 6,205,640.0 but strategy_total is 5,856,463.0 (gap -349,177.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 6,751,435.0 but strategy_total is 6,651,435.0 (gap -100,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31792,13 +31913,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>programs sum to 19,608,348.0 but strategy_total is 14,084,411.0 (gap -5,523,937.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 4,758,206.0 but strategy_total is 4,756,586.0 (gap -1,620.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31820,13 +31941,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>programs sum to 6,974,892.0 but strategy_total is 6,134,940.0 (gap -839,952.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 145,655,364.0 but strategy_total is 133,605,851.0 (gap -12,049,513.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31848,13 +31969,13 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>programs sum to 1,245,569.0 but strategy_total is 679,042.0 (gap -566,527.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 6,205,640.0 but strategy_total is 5,856,463.0 (gap -349,177.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31876,13 +31997,13 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>programs sum to 27,873,661.0 but strategy_total is 23,793,602.0 (gap -4,080,059.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 19,608,348.0 but strategy_total is 14,084,411.0 (gap -5,523,937.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -31904,109 +32025,97 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>programs sum to 26,555,683.0 but strategy_total is 20,778,896.0 (gap -5,776,787.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 6,974,892.0 but strategy_total is 6,134,940.0 (gap -839,952.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>reconciliation_mismatch</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>03000</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>03000.1.99.001</t>
-        </is>
-      </c>
+          <t>53038</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>program '03000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>programs sum to 1,245,569.0 but strategy_total is 679,042.0 (gap -566,527.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>reconciliation_mismatch</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>05000</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>05000.1.99.001</t>
-        </is>
-      </c>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>program '05000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>programs sum to 27,873,661.0 but strategy_total is 23,793,602.0 (gap -4,080,059.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>reconciliation_mismatch</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>05000</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>05000.1.99.157</t>
-        </is>
-      </c>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>program '05000.1.99.157' (Government Audit Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>programs sum to 26,555,683.0 but strategy_total is 20,778,896.0 (gap -5,776,787.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -32028,17 +32137,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>06000</t>
+          <t>03000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>06000.1.03.001</t>
+          <t>03000.1.99.001</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>program '06000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '03000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32060,17 +32169,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>06000</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>06000.1.03.158</t>
+          <t>05000.1.99.001</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>program '06000.1.03.158' (Public Service Personnel Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '05000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32092,17 +32201,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>07000.1.99.001</t>
+          <t>05000.1.99.157</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>program '07000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '05000.1.99.157' (Government Audit Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32124,17 +32233,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>06000</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>07000.1.99.139</t>
+          <t>06000.1.03.001</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>program '07000.1.99.139' (Protection of Children's Rights) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '06000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32156,17 +32265,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>06000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>07000.1.99.159</t>
+          <t>06000.1.03.158</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>program '07000.1.99.159' (Combatting Human Trafficking) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '06000.1.03.158' (Public Service Personnel Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32188,17 +32297,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15000.6.01.186</t>
+          <t>07000.1.99.001</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>program '15000.6.01.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '07000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32220,17 +32329,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15000.6.99.186</t>
+          <t>07000.1.99.139</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>program '15000.6.99.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '07000.1.99.139' (Protection of Children's Rights) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32252,17 +32361,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16000.1.01.001</t>
+          <t>07000.1.99.159</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>program '16000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '07000.1.99.159' (Combatting Human Trafficking) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32284,17 +32393,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19000.6.01.016</t>
+          <t>15000.6.01.186</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>program '19000.6.01.016' (Investment Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.01.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32316,17 +32425,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19000.6.04.185</t>
+          <t>15000.6.99.186</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>program '19000.6.04.185' (Environmental Management and Climate Change) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.99.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32348,17 +32457,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19000.6.06.378</t>
+          <t>16000.1.01.001</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>program '19000.6.06.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '16000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32385,12 +32494,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19000.6.14.177</t>
+          <t>19000.6.01.016</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>program '19000.6.14.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.01.016' (Investment Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32417,12 +32526,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19000.6.99.378</t>
+          <t>19000.6.04.185</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>program '19000.6.99.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.185' (Environmental Management and Climate Change) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32444,17 +32553,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19047.1.01.177</t>
+          <t>19000.6.06.378</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>program '19047.1.01.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32476,17 +32585,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19047.1.03.001</t>
+          <t>19000.6.14.177</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>program '19047.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.14.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32508,17 +32617,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19047.1.03.177</t>
+          <t>19000.6.99.378</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>program '19047.1.03.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.99.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32540,17 +32649,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19050.1.06.001</t>
+          <t>19047.1.01.177</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>program '19050.1.06.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19047.1.01.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32572,17 +32681,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19050.1.06.174</t>
+          <t>19047.1.03.001</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>program '19050.1.06.174' (Roads Infrastructure Development and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19047.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32604,17 +32713,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20000.1.02.001</t>
+          <t>19047.1.03.177</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>program '20000.1.02.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19047.1.03.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32636,17 +32745,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20000.1.02.132</t>
+          <t>19050.1.06.001</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>program '20000.1.02.132' (Macrofiscal Policy and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19050.1.06.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32668,17 +32777,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20000.1.02.137</t>
+          <t>19050.1.06.174</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>program '20000.1.02.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19050.1.06.174' (Roads Infrastructure Development and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32705,12 +32814,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20000.1.03.138</t>
+          <t>20000.1.02.001</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>program '20000.1.03.138' (Public Service Management and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.02.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32737,12 +32846,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20000.1.05.142</t>
+          <t>20000.1.02.132</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>program '20000.1.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.02.132' (Macrofiscal Policy and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32769,12 +32878,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20000.1.99.001</t>
+          <t>20000.1.02.137</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>program '20000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.02.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32801,12 +32910,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20000.1.99.144</t>
+          <t>20000.1.03.138</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>program '20000.1.99.144' (Promotion of the Integrity of Contracts and Licenses) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.03.138' (Public Service Management and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32833,12 +32942,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20000.6.05.142</t>
+          <t>20000.1.05.142</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>program '20000.6.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32865,12 +32974,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20000.6.99.137</t>
+          <t>20000.1.99.001</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>program '20000.6.99.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32897,12 +33006,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20000.6.99.142</t>
+          <t>20000.1.99.144</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>program '20000.6.99.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.99.144' (Promotion of the Integrity of Contracts and Licenses) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32924,17 +33033,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>26000.1.01.436</t>
+          <t>20000.6.05.142</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>program '26000.1.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32956,17 +33065,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>26000.1.01.437</t>
+          <t>20000.6.99.137</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>program '26000.1.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.99.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -32988,17 +33097,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>26000.6.01.436</t>
+          <t>20000.6.99.142</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>program '26000.6.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.99.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33025,12 +33134,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>26000.6.01.437</t>
+          <t>26000.1.01.436</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>program '26000.6.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33052,17 +33161,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>26022.1.01.001</t>
+          <t>26000.1.01.437</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>program '26022.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33084,17 +33193,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>26022.1.01.420</t>
+          <t>26000.6.01.436</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>program '26022.1.01.420' (Public Safety and Internal Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33116,17 +33225,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>26053.1.01.001</t>
+          <t>26000.6.01.437</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>program '26053.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33148,17 +33257,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>26053.1.01.438</t>
+          <t>26022.1.01.001</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>program '26053.1.01.438' (Travel and Identity Facilitation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26022.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33180,17 +33289,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>26059.1.01.001</t>
+          <t>26022.1.01.420</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>program '26059.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26022.1.01.420' (Public Safety and Internal Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33212,17 +33321,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>28030.1.03.001</t>
+          <t>26053.1.01.001</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>program '28030.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26053.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33244,17 +33353,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>28031.1.03.001</t>
+          <t>26053.1.01.438</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>program '28031.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26053.1.01.438' (Travel and Identity Facilitation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33276,17 +33385,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>28058</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>28058.1.03.427</t>
+          <t>26059.1.01.001</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>program '28058.1.03.427' (Administration of Justice) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26059.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33308,17 +33417,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>30000.1.04.001</t>
+          <t>28030.1.03.001</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>program '30000.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28030.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33340,17 +33449,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>28031</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>30000.1.04.150</t>
+          <t>28031.1.03.001</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>program '30000.1.04.150' (Management of Foreign Affairs) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28031.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33372,17 +33481,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>41051.1.04.001</t>
+          <t>28058.1.03.427</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>program '41051.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28058.1.03.427' (Administration of Justice) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33404,17 +33513,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>41051.1.04.326</t>
+          <t>30000.1.04.001</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>program '41051.1.04.326' (Children and Family Welfare Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '30000.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33436,17 +33545,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>42000.1.01.001</t>
+          <t>30000.1.04.150</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>program '42000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '30000.1.04.150' (Management of Foreign Affairs) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33468,17 +33577,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>42000.1.01.282</t>
+          <t>41051.1.04.001</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>program '42000.1.01.282' (Health Sector Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41051.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33500,17 +33609,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>42000.1.04.281</t>
+          <t>41051.1.04.326</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>program '42000.1.04.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41051.1.04.326' (Children and Family Welfare Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33537,12 +33646,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>42000.1.05.281</t>
+          <t>42000.1.01.001</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>program '42000.1.05.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33569,12 +33678,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>42000.6.01.281</t>
+          <t>42000.1.01.282</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>program '42000.6.01.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.01.282' (Health Sector Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33596,17 +33705,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>46000.1.01.001</t>
+          <t>42000.1.04.281</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>program '46000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.04.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33628,17 +33737,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>46000.1.01.268</t>
+          <t>42000.1.05.281</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>program '46000.1.01.268' (Development and Promotion of Sports and Recreation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.05.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33660,17 +33769,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>46000.1.02.265</t>
+          <t>42000.6.01.281</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>program '46000.1.02.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.6.01.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33697,12 +33806,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>46000.1.03.265</t>
+          <t>46000.1.01.001</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>program '46000.1.03.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33729,12 +33838,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>46000.1.13.267</t>
+          <t>46000.1.01.268</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>program '46000.1.13.267' (Entertainment Economic Linkages) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.01.268' (Development and Promotion of Sports and Recreation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33761,12 +33870,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>46000.1.99.266</t>
+          <t>46000.1.02.265</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>program '46000.1.99.266' (Gender Mainstreaming) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.02.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33788,17 +33897,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>51000.1.03.001</t>
+          <t>46000.1.03.265</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>program '51000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.03.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33820,17 +33929,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>51000.1.03.181</t>
+          <t>46000.1.13.267</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>program '51000.1.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.13.267' (Entertainment Economic Linkages) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33852,17 +33961,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>51000.6.03.181</t>
+          <t>46000.1.99.266</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>program '51000.6.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.99.266' (Gender Mainstreaming) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33884,17 +33993,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>53000.1.01.182</t>
+          <t>51000.1.03.001</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>program '53000.1.01.182' (Industrial Development and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33916,17 +34025,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>53000.1.01.184</t>
+          <t>51000.1.03.181</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>program '53000.1.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33948,17 +34057,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>53000.6.01.184</t>
+          <t>51000.6.03.181</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>program '53000.6.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.6.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -33980,17 +34089,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>53038.1.01.001</t>
+          <t>53000.1.01.182</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>program '53038.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.182' (Industrial Development and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34012,17 +34121,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>53038.1.01.156</t>
+          <t>53000.1.01.184</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>program '53038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34044,17 +34153,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>72000.1.99.013</t>
+          <t>53000.6.01.184</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>program '72000.1.99.013' (Local Government Oversight) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.6.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34071,22 +34180,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2019,2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>10000.1.01.001</t>
+          <t>53038.1.01.001</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>program '10000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53038.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34103,22 +34212,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2019,2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>10000.1.99.730</t>
+          <t>53038.1.01.156</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>program '10000.1.99.730' (Independent Oversight of Fiscal Policies and Fiscal Performance) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34135,22 +34244,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2019,2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15039.1.11.001</t>
+          <t>72000.1.99.013</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>program '15039.1.11.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.013' (Local Government Oversight) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34172,17 +34281,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>15039.1.11.555</t>
+          <t>10000.1.01.001</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>program '15039.1.11.555' (Postal Operations and Courier Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '10000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34204,17 +34313,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16000.1.01.187</t>
+          <t>10000.1.99.730</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>program '16000.1.01.187' (Public Sector Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '10000.1.99.730' (Independent Oversight of Fiscal Policies and Fiscal Performance) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34236,17 +34345,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>19000.1.01.379</t>
+          <t>15039.1.11.001</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>program '19000.1.01.379' (Housing and Urban Renewal) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15039.1.11.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34268,17 +34377,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>19000.1.03.378</t>
+          <t>15039.1.11.555</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>program '19000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15039.1.11.555' (Postal Operations and Courier Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34300,17 +34409,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19000.1.06.378</t>
+          <t>16000.1.01.187</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>program '19000.1.06.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '16000.1.01.187' (Public Sector Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34337,12 +34446,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19000.1.14.378</t>
+          <t>19000.1.01.379</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>program '19000.1.14.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.01.379' (Housing and Urban Renewal) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34369,12 +34478,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>19000.1.15.185</t>
+          <t>19000.1.03.378</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>program '19000.1.15.185' (Environmental Management and Climate Change) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34401,12 +34510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>19000.1.99.001</t>
+          <t>19000.1.06.378</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>program '19000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.06.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34433,12 +34542,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>19000.6.03.378</t>
+          <t>19000.1.14.378</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>program '19000.6.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.14.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34460,17 +34569,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>20000.6.06.137</t>
+          <t>19000.1.15.185</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>program '20000.6.06.137' (Management of Public Finances) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.15.185' (Environmental Management and Climate Change) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34492,17 +34601,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>20011.1.02.47</t>
+          <t>19000.1.99.001</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>program '20011.1.02.47' (Treasury Planning and Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34524,17 +34633,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>20060.1.02.189</t>
+          <t>19000.6.03.378</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>program '20060.1.02.189' (Management of Financial Crimes) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34556,17 +34665,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>20061.1.02.190</t>
+          <t>20000.6.06.137</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>program '20061.1.02.190' (Government Revenue Protection and Compliance Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.06.137' (Management of Public Finances) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34588,17 +34697,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>28058</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>28058.1.03.012</t>
+          <t>20011.1.02.47</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>program '28058.1.03.012' (Judiciary Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20011.1.02.47' (Treasury Planning and Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34620,17 +34729,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>40000.1.01.325</t>
+          <t>20060.1.02.189</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>program '40000.1.01.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20060.1.02.189' (Management of Financial Crimes) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34652,17 +34761,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>40000.1.02.001</t>
+          <t>20061.1.02.190</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>program '40000.1.02.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20061.1.02.190' (Government Revenue Protection and Compliance Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34684,17 +34793,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>40000.1.02.325</t>
+          <t>28058.1.03.012</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>program '40000.1.02.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28058.1.03.012' (Judiciary Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34721,12 +34830,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>40000.1.02.726</t>
+          <t>40000.1.01.325</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>program '40000.1.02.726' ((formerly Promotion and Supervision)) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.01.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34753,12 +34862,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>40000.1.02.729</t>
+          <t>40000.1.02.001</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>program '40000.1.02.729' (National Productivity) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34785,12 +34894,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>40000.1.03.325</t>
+          <t>40000.1.02.325</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>program '40000.1.03.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34817,12 +34926,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>40000.1.99.325</t>
+          <t>40000.1.02.726</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>program '40000.1.99.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.726' ((formerly Promotion and Supervision)) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34849,12 +34958,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>40000.1.99.328</t>
+          <t>40000.1.02.729</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>program '40000.1.99.328' (Social Security Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.729' (National Productivity) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34876,17 +34985,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>41000.6.04.261</t>
+          <t>40000.1.03.325</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>program '41000.6.04.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.03.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34908,17 +35017,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>41000.6.06.261</t>
+          <t>40000.1.99.325</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>program '41000.6.06.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.99.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34940,17 +35049,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>51000.1.05.179</t>
+          <t>40000.1.99.328</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>program '51000.1.05.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.99.328' (Social Security Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34972,17 +35081,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>51000.1.15.179</t>
+          <t>41000.6.04.261</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>program '51000.1.15.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.6.04.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35004,17 +35113,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>53000.1.01.001</t>
+          <t>41000.6.06.261</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>program '53000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.6.06.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35036,17 +35145,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>53000.1.01.183</t>
+          <t>51000.1.05.179</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>program '53000.1.01.183' (Consumer and Public Protection) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.05.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35068,17 +35177,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>69000.1.04.701</t>
+          <t>51000.1.15.179</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>program '69000.1.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.15.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35100,17 +35209,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>69000.1.06.178</t>
+          <t>53000.1.01.001</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>program '69000.1.06.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35132,17 +35241,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>69000.1.07.178</t>
+          <t>53000.1.01.183</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>program '69000.1.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.183' (Consumer and Public Protection) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35169,12 +35278,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>69000.1.09.178</t>
+          <t>69000.1.04.701</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>program '69000.1.09.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35201,12 +35310,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>69000.1.10.178</t>
+          <t>69000.1.06.178</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>program '69000.1.10.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.06.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35233,12 +35342,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>69000.1.12.128</t>
+          <t>69000.1.07.178</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>program '69000.1.12.128' (ICT Development, Access and Use) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35265,12 +35374,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>69000.1.15.003</t>
+          <t>69000.1.09.178</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>program '69000.1.15.003' (Research and Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.09.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35297,12 +35406,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>69000.1.15.129</t>
+          <t>69000.1.10.178</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>program '69000.1.15.129' (Science, Technology and Innovation Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.10.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35329,12 +35438,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>69000.1.99.001</t>
+          <t>69000.1.12.128</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>program '69000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.12.128' (ICT Development, Access and Use) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35361,12 +35470,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>69000.6.04.701</t>
+          <t>69000.1.15.003</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>program '69000.6.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.15.003' (Research and Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35393,12 +35502,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>69000.6.07.178</t>
+          <t>69000.1.15.129</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>program '69000.6.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.15.129' (Science, Technology and Innovation Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35420,17 +35529,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>72000.1.01.013</t>
+          <t>69000.1.99.001</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>program '72000.1.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35452,17 +35561,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>72000.1.02.014</t>
+          <t>69000.6.04.701</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>program '72000.1.02.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.6.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35484,17 +35593,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>72000.1.02.015</t>
+          <t>69000.6.07.178</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>program '72000.1.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.6.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35521,12 +35630,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>72000.1.03.378</t>
+          <t>72000.1.01.013</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>program '72000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35553,12 +35662,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>72000.1.06.013</t>
+          <t>72000.1.02.014</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>program '72000.1.06.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.02.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35585,12 +35694,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>72000.1.99.001</t>
+          <t>72000.1.02.015</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>program '72000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35617,12 +35726,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>72000.1.99.014</t>
+          <t>72000.1.03.378</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>program '72000.1.99.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35649,12 +35758,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>72000.6.01.013</t>
+          <t>72000.1.06.013</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>program '72000.6.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.06.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35681,12 +35790,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>72000.6.02.015</t>
+          <t>72000.1.99.001</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>program '72000.6.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35703,22 +35812,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2019,2024</t>
+          <t>2019,2022</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>15010.1.03.001</t>
+          <t>72000.1.99.014</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>program '15010.1.03.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35735,22 +35844,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2019,2024</t>
+          <t>2019,2022</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>15010.1.03.468</t>
+          <t>72000.6.01.013</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>program '15010.1.03.468' (Government Information and Communication Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.6.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35767,22 +35876,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2019,2024</t>
+          <t>2019,2022</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>19000.6.04.378</t>
+          <t>72000.6.02.015</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>program '19000.6.04.378' (Land, Infrastructure and Physical Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.6.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35804,17 +35913,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>20000.6.02.137</t>
+          <t>15010.1.03.001</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>program '20000.6.02.137' (Management of Public Finances) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15010.1.03.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35836,17 +35945,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>26059.1.01.439</t>
+          <t>15010.1.03.468</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>program '26059.1.01.439' (Corruption and Cyber Threat Management) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15010.1.03.468' (Government Information and Communication Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35868,17 +35977,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>27000.1.01.001</t>
+          <t>19000.6.04.378</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>program '27000.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.378' (Land, Infrastructure and Physical Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35900,17 +36009,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>27000.1.01.188</t>
+          <t>20000.6.02.137</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>program '27000.1.01.188' (Facilitation of Law Reform) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.02.137' (Management of Public Finances) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35932,17 +36041,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>41000.1.22.24</t>
+          <t>26059.1.01.439</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>program '41000.1.22.24' (25) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26059.1.01.439' (Corruption and Cyber Threat Management) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35964,17 +36073,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>42034.1.01.001</t>
+          <t>27000.1.01.001</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>program '42034.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '27000.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35996,17 +36105,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>42034.1.01.175</t>
+          <t>27000.1.01.188</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>program '42034.1.01.175' (Mental Health Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '27000.1.01.188' (Facilitation of Law Reform) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36028,17 +36137,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>42035.1.01.001</t>
+          <t>41000.1.22.24</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>program '42035.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.22.24' (25) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36060,17 +36169,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>42034</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>42035.1.01.176</t>
+          <t>42034.1.01.001</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>program '42035.1.01.176' (Chemistry Support Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42034.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36092,17 +36201,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42034</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>56000.1.04.701</t>
+          <t>42034.1.01.175</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>program '56000.1.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42034.1.01.175' (Mental Health Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36124,17 +36233,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>56000.1.12.128</t>
+          <t>42035.1.01.001</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>program '56000.1.12.128' (ICT Development, Access and Use) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42035.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36156,17 +36265,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>56000.1.15.003</t>
+          <t>42035.1.01.176</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>program '56000.1.15.003' (Research and Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42035.1.01.176' (Chemistry Support Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36193,12 +36302,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>56000.1.15.129</t>
+          <t>56000.1.04.701</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>program '56000.1.15.129' (Science, Technology and Innovation Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36225,12 +36334,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>56000.1.99.001</t>
+          <t>56000.1.12.128</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>program '56000.1.99.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.12.128' (ICT Development, Access and Use) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36257,12 +36366,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>56000.6.04.701</t>
+          <t>56000.1.15.003</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>program '56000.6.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.15.003' (Research and Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36284,17 +36393,17 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>56039.1.11.555</t>
+          <t>56000.1.15.129</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>program '56039.1.11.555' (Postal Operations and Courier Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.15.129' (Science, Technology and Innovation Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36311,22 +36420,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019,2024</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>20011.1.02.001</t>
+          <t>56000.1.99.001</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>program '20011.1.02.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.99.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36343,22 +36452,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019,2024</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>26024.1.04.001</t>
+          <t>56000.6.04.701</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>program '26024.1.04.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.6.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36375,22 +36484,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2022,2024</t>
+          <t>2019,2024</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>56039</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>15000.6.01.145</t>
+          <t>56039.1.11.555</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>program '15000.6.01.145' (Corporate Office of the Prime Minister) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56039.1.11.555' (Postal Operations and Courier Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36407,22 +36516,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2022,2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>15000.6.04.701</t>
+          <t>20011.1.02.001</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>program '15000.6.04.701' (Energy Conservation and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20011.1.02.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36439,22 +36548,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2022,2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>15000.6.99.011</t>
+          <t>26024.1.04.001</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>program '15000.6.99.011' (Poverty Alleviation Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26024.1.04.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36476,17 +36585,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>16000.6.99.152</t>
+          <t>15000.6.01.145</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>program '16000.6.99.152' (Public Sector Reform Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.01.145' (Corporate Office of the Prime Minister) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36508,17 +36617,17 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>17000.1.13.001</t>
+          <t>15000.6.04.701</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>program '17000.1.13.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.04.701' (Energy Conservation and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36540,17 +36649,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>17000.1.13.652</t>
+          <t>15000.6.99.011</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>program '17000.1.13.652' (Tourism Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.99.011' (Poverty Alleviation Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36572,17 +36681,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>19000.6.01.301</t>
+          <t>16000.6.99.152</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>program '19000.6.01.301' (Industrial Development and Export Promotion) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '16000.6.99.152' (Public Sector Reform Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36604,17 +36713,17 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>19000.6.03.479</t>
+          <t>17000.1.13.001</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>program '19000.6.03.479' (Surveys and Investigations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '17000.1.13.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36636,17 +36745,17 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>19000.6.03.480</t>
+          <t>17000.1.13.652</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>program '19000.6.03.480' (Rural Water Supply Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '17000.1.13.652' (Tourism Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36673,12 +36782,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>19000.6.04.001</t>
+          <t>19000.6.01.301</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>program '19000.6.04.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.01.301' (Industrial Development and Export Promotion) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36705,12 +36814,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>19000.6.04.625</t>
+          <t>19000.6.03.479</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>program '19000.6.04.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.03.479' (Surveys and Investigations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36737,12 +36846,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>19000.6.06.005</t>
+          <t>19000.6.03.480</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>program '19000.6.06.005' (Disaster Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.03.480' (Rural Water Supply Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36769,12 +36878,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>19000.6.06.225</t>
+          <t>19000.6.04.001</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>program '19000.6.06.225' (Arterial Roads) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36801,12 +36910,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>19000.6.06.228</t>
+          <t>19000.6.04.625</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>program '19000.6.06.228' (Urban Roads, Kingston and St. Andrew) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36833,12 +36942,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>19000.6.06.377</t>
+          <t>19000.6.06.005</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>program '19000.6.06.377' (Area Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.005' (Disaster Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36865,12 +36974,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>19000.6.14.376</t>
+          <t>19000.6.06.225</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>program '19000.6.14.376' (Land Use Planning and Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.225' (Arterial Roads) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36897,12 +37006,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>19000.6.15.600</t>
+          <t>19000.6.06.228</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>program '19000.6.15.600' (Meteorological, Weather and Climate Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.228' (Urban Roads, Kingston and St. Andrew) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36929,12 +37038,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>19000.6.99.001</t>
+          <t>19000.6.06.377</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>program '19000.6.99.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.377' (Area Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36961,12 +37070,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>19000.6.99.625</t>
+          <t>19000.6.14.376</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>program '19000.6.99.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.14.376' (Land Use Planning and Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36988,17 +37097,17 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>20011.1.02.147</t>
+          <t>19000.6.15.600</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>program '20011.1.02.147' (Treasury Planning and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.15.600' (Meteorological, Weather and Climate Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37020,17 +37129,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>20019.1.03.100</t>
+          <t>19000.6.99.001</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>program '20019.1.03.100' (Crop/Livestock) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.99.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37052,17 +37161,17 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>20019.1.08.550</t>
+          <t>19000.6.99.625</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>program '20019.1.08.550' (Railway Operations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.99.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37084,17 +37193,17 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>26000.1.01.327</t>
+          <t>20011.1.02.147</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>program '26000.1.01.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20011.1.02.147' (Treasury Planning and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37116,17 +37225,17 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>26000.1.01.400</t>
+          <t>20019.1.03.100</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>program '26000.1.01.400' (Defense Forces Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20019.1.03.100' (Crop/Livestock) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37148,17 +37257,17 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>26000.1.01.425</t>
+          <t>20019.1.08.550</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>program '26000.1.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20019.1.08.550' (Railway Operations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37185,12 +37294,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>26000.1.01.426</t>
+          <t>26000.1.01.327</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>program '26000.1.01.426' (Legal Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37217,12 +37326,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>26000.6.01.425</t>
+          <t>26000.1.01.400</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>program '26000.6.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.400' (Defense Forces Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37249,12 +37358,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>26000.6.04.428</t>
+          <t>26000.1.01.425</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>program '26000.6.04.428' (Adult Institutions) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37281,12 +37390,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>26000.6.04.431</t>
+          <t>26000.1.01.426</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>program '26000.6.04.431' (Prevention and Rehabilitation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.426' (Legal Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37308,17 +37417,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>28052.1.03.155</t>
+          <t>26000.6.01.425</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>program '28052.1.03.155' (Law Reforms) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37340,17 +37449,17 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>28054.1.03.012</t>
+          <t>26000.6.04.428</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>program '28054.1.03.012' (Judiciary Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.04.428' (Adult Institutions) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37372,17 +37481,17 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>28054.1.03.427</t>
+          <t>26000.6.04.431</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>program '28054.1.03.427' (Administration of Justice) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.04.431' (Prevention and Rehabilitation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37404,17 +37513,17 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>41000.1.01.001</t>
+          <t>28052.1.03.155</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>program '41000.1.01.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28052.1.03.155' (Law Reforms) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37436,17 +37545,17 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>41000.1.01.007</t>
+          <t>28054.1.03.012</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>program '41000.1.01.007' (School Improvement Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28054.1.03.012' (Judiciary Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37468,17 +37577,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>41000.1.02.250</t>
+          <t>28054.1.03.427</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>program '41000.1.02.250' (Delivery of Early Childhood Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28054.1.03.427' (Administration of Justice) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37505,12 +37614,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>41000.1.03.251</t>
+          <t>41000.1.01.001</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>program '41000.1.03.251' (Delivery of Primary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.01.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37537,12 +37646,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>41000.1.03.465</t>
+          <t>41000.1.01.007</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>program '41000.1.03.465' (Preservation of Official and Other Permanent Records) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.01.007' (School Improvement Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37569,12 +37678,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>41000.1.03.468</t>
+          <t>41000.1.02.250</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>program '41000.1.03.468' (Government Information and Communication Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.02.250' (Delivery of Early Childhood Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37601,12 +37710,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>41000.1.04.252</t>
+          <t>41000.1.03.251</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>program '41000.1.04.252' (Delivery of Secondary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.03.251' (Delivery of Primary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37633,12 +37742,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>41000.1.04.254</t>
+          <t>41000.1.03.465</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>program '41000.1.04.254' (Delivery of Technical/Vocational Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.03.465' (Preservation of Official and Other Permanent Records) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37665,12 +37774,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>41000.1.04.326</t>
+          <t>41000.1.03.468</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>program '41000.1.04.326' (Children and Family Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.03.468' (Government Information and Communication Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37697,12 +37806,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>41000.1.05.253</t>
+          <t>41000.1.04.252</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>program '41000.1.05.253' (Delivery of Tertiary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.04.252' (Delivery of Secondary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37729,12 +37838,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>41000.1.05.256</t>
+          <t>41000.1.04.254</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>program '41000.1.05.256' (Teachers Education and Training) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.04.254' (Delivery of Technical/Vocational Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37761,12 +37870,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>41000.1.05.500</t>
+          <t>41000.1.04.326</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>program '41000.1.05.500' (Youth Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.04.326' (Children and Family Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37793,12 +37902,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>41000.1.06.255</t>
+          <t>41000.1.05.253</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>program '41000.1.06.255' (Delivery of Special Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.05.253' (Delivery of Tertiary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37825,12 +37934,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>41000.1.07.004</t>
+          <t>41000.1.05.256</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>program '41000.1.07.004' (Regional and International Cooperation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.05.256' (Teachers Education and Training) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37857,12 +37966,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>41000.1.07.258</t>
+          <t>41000.1.05.500</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>program '41000.1.07.258' (Core Educational Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.05.500' (Youth Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37889,12 +37998,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>41000.1.07.259</t>
+          <t>41000.1.06.255</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>program '41000.1.07.259' (Library Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.06.255' (Delivery of Special Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37921,12 +38030,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>41000.1.07.260</t>
+          <t>41000.1.07.004</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>program '41000.1.07.260' (Nutrition) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.004' (Regional and International Cooperation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37948,17 +38057,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>42000.1.05.327</t>
+          <t>41000.1.07.258</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>program '42000.1.05.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.258' (Core Educational Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37980,17 +38089,17 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>46000.6.99.325</t>
+          <t>41000.1.07.259</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>program '46000.6.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.259' (Library Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38012,17 +38121,17 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>50038.1.01.156</t>
+          <t>41000.1.07.260</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>program '50038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.260' (Nutrition) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38044,17 +38153,17 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>56000.6.11.128</t>
+          <t>42000.1.05.327</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>program '56000.6.11.128' (ICT Development, Access and Use) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.05.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38076,17 +38185,17 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>68000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>68000.6.07.178</t>
+          <t>46000.6.99.325</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>program '68000.6.07.178' (Transport Management and Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.6.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38108,17 +38217,17 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>72000.1.99.325</t>
+          <t>50038.1.01.156</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>program '72000.1.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38135,22 +38244,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022,2024</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>02000</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>02000.1.01.001</t>
+          <t>56000.6.11.128</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>program '02000.1.01.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.6.11.128' (ICT Development, Access and Use) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38167,22 +38276,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022,2024</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>02000</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>02000.1.01.164</t>
+          <t>68000.6.07.178</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>program '02000.1.01.164' (Legislative Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '68000.6.07.178' (Transport Management and Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38199,22 +38308,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022,2024</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>02000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>02000.1.01.165</t>
+          <t>72000.1.99.325</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>program '02000.1.01.165' (Political and Electoral Dispute Resolution) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38236,17 +38345,17 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>02000</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>20056.1.02.001</t>
+          <t>02000.1.01.001</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>program '20056.1.02.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '02000.1.01.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38268,17 +38377,17 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>02000</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>20056.1.02.149</t>
+          <t>02000.1.01.164</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>program '20056.1.02.149' (Domestic Tax Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '02000.1.01.164' (Legislative Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38300,153 +38409,249 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>02000</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>26000.6.01.400</t>
+          <t>02000.1.01.165</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>program '26000.6.01.400' (Defence Force Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '02000.1.01.165' (Political and Electoral Dispute Resolution) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>large_yoy_swing</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2019-&gt;2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>26000.1.01.001</t>
+          <t>20056.1.02.001</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>program '26000.1.01.001' changed +226% (2,116,532.0 -&gt; 6,902,991.0) - verify this is real and not an extraction error.</t>
+          <t>program '20056.1.02.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>large_yoy_swing</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2022-&gt;2024</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>20000.6.99.137</t>
+          <t>20056.1.02.149</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>program '20000.6.99.137' changed +223% (7,603,835.0 -&gt; 24,535,325.0) - verify this is real and not an extraction error.</t>
+          <t>program '20056.1.02.149' (Domestic Tax Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>26000.6.01.400</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>national budget total = 278,267,320.0</t>
+          <t>program '26000.6.01.400' (Defence Force Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>large_yoy_swing</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
+          <t>2019-&gt;2022</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>26000.1.01.001</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>national budget total = 302,576,866.0</t>
+          <t>program '26000.1.01.001' changed +226% (2,116,532.0 -&gt; 6,902,991.0) - verify this is real and not an extraction error.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>large_yoy_swing</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2022-&gt;2024</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>20000.6.99.137</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>program '20000.6.99.137' changed +223% (7,603,835.0 -&gt; 24,535,325.0) - verify this is real and not an extraction error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>national_total</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>national budget total = 239,480,965.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>national budget total = 404,258,046.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>national budget total = 458,257,529.0</t>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>national budget total = 639,705,043.0</t>
         </is>
       </c>
     </row>

--- a/jamaica/budget_layer_all_years.xlsx
+++ b/jamaica/budget_layer_all_years.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M421"/>
+  <dimension ref="A1:N421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,11 @@
           <t>strategy_name_source</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>countable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,6 +528,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,6 +584,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,6 +644,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -688,6 +704,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -743,6 +764,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -798,6 +824,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,6 +866,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -890,6 +922,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -945,6 +982,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -982,6 +1024,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1037,6 +1080,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1092,6 +1140,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1129,6 +1182,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,6 +1238,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1239,6 +1298,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1294,6 +1358,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1331,6 +1400,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1373,6 +1443,7 @@
           <t>Registrar General's Department and Island Records Office</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1428,6 +1499,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1483,6 +1559,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1543,6 +1624,11 @@
           <t>Office of the Cabinet" --&gt;</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1580,6 +1666,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1635,6 +1722,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1690,6 +1782,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1727,6 +1824,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1782,6 +1880,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1837,6 +1940,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1874,6 +1982,7 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1929,6 +2038,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1984,6 +2098,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2039,6 +2158,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2094,6 +2218,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2149,6 +2278,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2204,6 +2338,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2259,6 +2398,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2314,6 +2458,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2369,6 +2518,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2424,6 +2578,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2479,6 +2638,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2534,6 +2698,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2589,6 +2758,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2626,6 +2800,7 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2681,6 +2856,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2736,6 +2916,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2791,6 +2976,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2846,6 +3036,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2901,6 +3096,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2956,6 +3156,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3011,6 +3216,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3066,6 +3276,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3121,6 +3336,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3158,6 +3378,7 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3213,6 +3434,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3266,6 +3492,11 @@
       <c r="L55" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3310,6 +3541,7 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3365,6 +3597,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3420,6 +3657,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3475,6 +3717,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3530,6 +3777,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3585,6 +3837,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3645,6 +3902,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3705,6 +3967,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3765,6 +4032,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3825,6 +4097,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3862,6 +4139,7 @@
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3899,6 +4177,7 @@
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3954,6 +4233,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4009,6 +4293,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4046,6 +4335,7 @@
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4088,6 +4378,7 @@
           <t>Ministry of Justice" --&gt;</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4143,6 +4434,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4198,6 +4494,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4258,6 +4559,11 @@
           <t>Ministry of Justice" --&gt;</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4295,6 +4601,7 @@
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4350,6 +4657,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4405,6 +4717,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4460,6 +4777,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4515,6 +4837,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4570,6 +4897,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4607,6 +4939,7 @@
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4649,6 +4982,7 @@
           <t>Ministry of Education, Youth and Information.</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4709,6 +5043,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4769,6 +5108,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4829,6 +5173,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4889,6 +5238,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4949,6 +5303,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5009,6 +5368,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5069,6 +5433,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5129,6 +5498,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5189,6 +5563,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5249,6 +5628,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5309,6 +5693,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5369,6 +5758,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5429,6 +5823,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5489,6 +5888,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5549,6 +5953,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5609,6 +6018,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5669,6 +6083,11 @@
           <t>Ministry of Education, Youth and Information</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5729,6 +6148,11 @@
           <t>Ministry of Health</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5789,6 +6213,11 @@
           <t>Ministry of Culture, Gender, Entertainment and Sport" --&gt;</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5826,6 +6255,7 @@
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5863,6 +6293,7 @@
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5918,6 +6349,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5955,6 +6391,7 @@
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6010,6 +6447,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6063,6 +6505,11 @@
       <c r="L107" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -6107,6 +6554,7 @@
           <t>Ministry of Local Government and Community Development" --&gt;</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6162,6 +6610,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6199,6 +6652,7 @@
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6254,6 +6708,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6309,6 +6768,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6364,6 +6828,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6419,6 +6888,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6474,6 +6948,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6529,6 +7008,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6566,6 +7050,7 @@
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6621,6 +7106,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6676,6 +7166,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6731,6 +7226,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6786,6 +7286,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6841,6 +7346,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6896,6 +7406,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6951,6 +7466,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6988,6 +7508,7 @@
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7043,6 +7564,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7098,6 +7624,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7135,6 +7666,7 @@
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7190,6 +7722,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7245,6 +7782,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7282,6 +7824,7 @@
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7337,6 +7880,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7392,6 +7940,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7429,6 +7982,7 @@
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7484,6 +8038,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7537,6 +8096,11 @@
       <c r="L136" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -7581,6 +8145,7 @@
           <t>Registrar General's Department and Island Records Office</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7636,6 +8201,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7691,6 +8261,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7746,6 +8321,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7783,6 +8363,7 @@
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7838,6 +8419,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7891,6 +8477,11 @@
       <c r="L143" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -7935,6 +8526,7 @@
           <t>Ministry of Tourism Budget 1 - Recurrent Function 04 - Economic Affairs SubFunction 13 - Tourism Programme 652 - Tourism Development" --&gt;</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7972,6 +8564,7 @@
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8027,6 +8620,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8082,6 +8680,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8137,6 +8740,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8192,6 +8800,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8247,6 +8860,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8302,6 +8920,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8339,6 +8962,7 @@
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8394,6 +9018,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8449,6 +9078,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8486,6 +9120,7 @@
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8541,6 +9176,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8596,6 +9236,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8651,6 +9296,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8688,6 +9338,7 @@
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8743,6 +9394,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8798,6 +9454,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8835,6 +9496,7 @@
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8895,6 +9557,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8955,6 +9622,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9015,6 +9687,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9075,6 +9752,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9135,6 +9817,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9195,6 +9882,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9255,6 +9947,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9310,6 +10007,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9365,6 +10067,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9420,6 +10127,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9475,6 +10187,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9530,6 +10247,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9585,6 +10307,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9640,6 +10367,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9695,6 +10427,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9748,6 +10485,11 @@
       <c r="L178" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -9792,6 +10534,7 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9847,6 +10590,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9902,6 +10650,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9957,6 +10710,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10017,6 +10775,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10077,6 +10840,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10137,6 +10905,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10174,6 +10947,7 @@
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10229,6 +11003,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10284,6 +11063,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10321,6 +11105,7 @@
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10376,6 +11161,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10413,6 +11203,7 @@
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10473,6 +11264,11 @@
           <t>Passport, Immigration and Citizenship Agency Budget 1 - Recurrent</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10533,6 +11329,11 @@
           <t>Passport, Immigration and Citizenship Agency Budget 1 - Recurrent</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10588,6 +11389,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10643,6 +11449,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10698,6 +11509,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10751,6 +11567,11 @@
       <c r="L197" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -10795,6 +11616,7 @@
           <t>Ministry of Justice" --&gt;</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10850,6 +11672,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10905,6 +11732,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10965,6 +11797,11 @@
           <t>Ministry of Justice" --&gt;</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11002,6 +11839,7 @@
       </c>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11057,6 +11895,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11112,6 +11955,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11167,6 +12015,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11222,6 +12075,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11277,6 +12135,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11314,6 +12177,7 @@
       </c>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11369,6 +12233,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11424,6 +12293,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11479,6 +12353,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11516,6 +12395,7 @@
       </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11571,6 +12451,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11624,6 +12509,11 @@
       <c r="L214" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -11668,6 +12558,7 @@
           <t>Minstry of Health and Wellness" --&gt;</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11723,6 +12614,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11778,6 +12674,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11833,6 +12734,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11888,6 +12794,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11948,6 +12859,11 @@
           <t>Minstry of Health and Wellness" --&gt;</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12003,6 +12919,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12058,6 +12979,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12113,6 +13039,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12166,6 +13097,11 @@
       <c r="L224" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -12210,6 +13146,7 @@
           <t>Ministry of Culture, Gender, Entertainment and Sport" --&gt;</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12265,6 +13202,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12320,6 +13262,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12375,6 +13322,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12430,6 +13382,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12485,6 +13442,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12538,6 +13500,11 @@
       <c r="L231" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -12582,6 +13549,7 @@
           <t>Ministry of Agriculture and Fisheries" --&gt;</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12637,6 +13605,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12692,6 +13665,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12750,6 +13728,11 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>Ministry of Agriculture and Fisheries" --&gt;</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -12794,6 +13777,7 @@
           <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12849,6 +13833,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12904,6 +13893,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12964,6 +13958,11 @@
           <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13001,6 +14000,7 @@
       </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13056,6 +14056,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13109,6 +14114,11 @@
       <c r="L242" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -13153,6 +14163,7 @@
           <t>Ministry of Science, Energy and Technology" --&gt;</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13213,6 +14224,11 @@
           <t>Ministry of Science, Energy and Technology</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13273,6 +14289,11 @@
           <t>Ministry of Science, Energy and Technology</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13333,6 +14354,11 @@
           <t>Ministry of Science, Energy and Technology</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13393,6 +14419,11 @@
           <t>Ministry of Science, Energy and Technology</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13453,6 +14484,11 @@
           <t>Ministry of Science, Energy and Technology</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13513,6 +14549,11 @@
           <t>Ministry of Science, Energy and Technology" --&gt;</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13550,6 +14591,7 @@
       </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13605,6 +14647,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13665,6 +14712,11 @@
           <t>Ministry of Local Government and Rural Development</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13702,6 +14754,7 @@
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13757,6 +14810,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13812,6 +14870,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13867,6 +14930,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13904,6 +14972,7 @@
       </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13959,6 +15028,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14014,6 +15088,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14069,6 +15148,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14124,6 +15208,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14179,6 +15268,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14234,6 +15328,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14289,6 +15388,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14326,6 +15430,7 @@
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14381,6 +15486,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14436,6 +15546,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14491,6 +15606,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14546,6 +15666,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14601,6 +15726,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14656,6 +15786,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14711,6 +15846,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14764,6 +15904,11 @@
       <c r="L273" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -14808,6 +15953,7 @@
           <t>Registrar General's Department and Island Records Office</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14863,6 +16009,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14918,6 +16069,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14955,6 +16111,7 @@
       </c>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15010,6 +16167,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15065,6 +16227,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15120,6 +16287,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15175,6 +16347,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15212,6 +16389,7 @@
       </c>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15267,6 +16445,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15322,6 +16505,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15359,6 +16547,7 @@
       </c>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15419,6 +16608,11 @@
           <t>Ministry of Economic Growth and Job Creation</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15479,6 +16673,11 @@
           <t>Ministry of Economic Growth and Job Creation</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15539,6 +16738,11 @@
           <t>Ministry of Economic Growth and Job Creation</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15599,6 +16803,11 @@
           <t>Ministry of Economic Growth and Job Creation</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15659,6 +16868,11 @@
           <t>Ministry of Economic Growth and Job Creation</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15719,6 +16933,11 @@
           <t>Ministry of Economic Growth and Job Creation</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15774,6 +16993,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15829,6 +17053,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15884,6 +17113,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15939,6 +17173,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15994,6 +17233,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16049,6 +17293,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16086,6 +17335,7 @@
       </c>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16141,6 +17391,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16196,6 +17451,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16233,6 +17493,7 @@
       </c>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16288,6 +17549,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16343,6 +17609,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -16398,6 +17669,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16435,6 +17711,7 @@
       </c>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16490,6 +17767,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16545,6 +17827,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16582,6 +17869,7 @@
       </c>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16642,6 +17930,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16702,6 +17995,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16762,6 +18060,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16822,6 +18125,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16882,6 +18190,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16942,6 +18255,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -17002,6 +18320,11 @@
           <t>Ministry of Finance and the Public Service</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -17057,6 +18380,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -17112,6 +18440,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17167,6 +18500,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17222,6 +18560,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -17277,6 +18620,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17332,6 +18680,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -17387,6 +18740,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17442,6 +18800,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -17497,6 +18860,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -17534,6 +18902,7 @@
       </c>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -17589,6 +18958,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -17642,6 +19016,11 @@
       <c r="L327" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -17686,6 +19065,7 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -17741,6 +19121,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -17796,6 +19181,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -17851,6 +19241,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -17911,6 +19306,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -17971,6 +19371,11 @@
           <t>Ministry of National Security" --&gt;</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -18008,6 +19413,7 @@
       </c>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18063,6 +19469,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -18118,6 +19529,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -18173,6 +19589,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18228,6 +19649,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18265,6 +19691,7 @@
       </c>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18320,6 +19747,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -18375,6 +19807,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -18412,6 +19849,7 @@
       </c>
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18465,6 +19903,11 @@
       <c r="L343" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -18509,6 +19952,7 @@
           <t>Ministry of Justice" --&gt;</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -18564,6 +20008,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -18619,6 +20068,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -18679,6 +20133,11 @@
           <t>Ministry of Justice" --&gt;</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -18716,6 +20175,7 @@
       </c>
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -18771,6 +20231,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -18826,6 +20291,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -18881,6 +20351,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -18936,6 +20411,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -18991,6 +20471,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -19046,6 +20531,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19083,6 +20573,7 @@
       </c>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -19138,6 +20629,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19193,6 +20689,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19248,6 +20749,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19303,6 +20809,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19358,6 +20869,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19413,6 +20929,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -19468,6 +20989,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -19523,6 +21049,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -19578,6 +21109,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19633,6 +21169,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19693,6 +21234,11 @@
           <t>Ministry of Education and Youth" --&gt;</t>
         </is>
       </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19753,6 +21299,11 @@
           <t>Ministry of Education and Youth" --&gt;</t>
         </is>
       </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19790,6 +21341,7 @@
       </c>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19850,6 +21402,11 @@
           <t>Child Protection and Family Services Agency Budget 1 - Recurrent</t>
         </is>
       </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -19908,6 +21465,11 @@
       <c r="M370" t="inlineStr">
         <is>
           <t>Child Protection and Family Services Agency Budget 1 - Recurrent</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -19952,6 +21514,7 @@
           <t>Ministry of Health and Wellness" --&gt;</t>
         </is>
       </c>
+      <c r="N371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -20007,6 +21570,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -20062,6 +21630,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -20117,6 +21690,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -20172,6 +21750,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -20232,6 +21815,11 @@
           <t>Ministry of Health and Wellness" --&gt;</t>
         </is>
       </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20269,6 +21857,7 @@
       </c>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -20324,6 +21913,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20379,6 +21973,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20434,6 +22033,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20489,6 +22093,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -20544,6 +22153,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -20597,6 +22211,11 @@
       <c r="L383" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -20641,6 +22260,7 @@
           <t>Ministry of Agriculture, Fisheries and Mining" --&gt;</t>
         </is>
       </c>
+      <c r="N384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20701,6 +22321,11 @@
           <t>Ministry of Agriculture, Fisheries and Mining</t>
         </is>
       </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20761,6 +22386,11 @@
           <t>Ministry of Agriculture, Fisheries and Mining</t>
         </is>
       </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20821,6 +22451,11 @@
           <t>Ministry of Agriculture, Fisheries and Mining</t>
         </is>
       </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -20881,6 +22516,11 @@
           <t>Ministry of Agriculture, Fisheries and Mining</t>
         </is>
       </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -20939,6 +22579,11 @@
       <c r="M389" t="inlineStr">
         <is>
           <t>Ministry of Agriculture, Fisheries and Mining" --&gt;</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -20983,6 +22628,7 @@
           <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
         </is>
       </c>
+      <c r="N390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -21038,6 +22684,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -21093,6 +22744,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -21148,6 +22804,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -21203,6 +22864,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21263,6 +22929,11 @@
           <t>Ministry of Industry, Investment and Commerce" --&gt;</t>
         </is>
       </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21300,6 +22971,7 @@
       </c>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21355,6 +23027,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21410,6 +23087,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21447,6 +23129,7 @@
       </c>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21507,6 +23190,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21567,6 +23255,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -21627,6 +23320,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21687,6 +23385,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21747,6 +23450,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21807,6 +23515,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21867,6 +23580,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21927,6 +23645,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21987,6 +23710,11 @@
           <t>Ministry of Science, Energy, Telecommunications and</t>
         </is>
       </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -22042,6 +23770,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -22095,6 +23828,11 @@
       <c r="L410" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -22139,6 +23877,7 @@
           <t>Ministry of Local Government and Community Development" --&gt;</t>
         </is>
       </c>
+      <c r="N411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -22194,6 +23933,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -22249,6 +23993,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22304,6 +24053,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22359,6 +24113,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22414,6 +24173,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22469,6 +24233,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22524,6 +24293,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22579,6 +24353,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -22639,6 +24418,11 @@
           <t>Ministry of Local Government and Community Development" --&gt;</t>
         </is>
       </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -22697,6 +24481,11 @@
       <c r="M421" t="inlineStr">
         <is>
           <t>Ministry of Local Government and Community Development" --&gt;</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>

--- a/jamaica/budget_layer_all_years.xlsx
+++ b/jamaica/budget_layer_all_years.xlsx
@@ -29497,7 +29497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29518,20 +29518,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>grand_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>extracted_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>gap_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>nested_heads</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>national</t>
         </is>
@@ -29549,18 +29559,20 @@
       <c r="C2" t="n">
         <v>239480965</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
         <v>13.94</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>programmes</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>239480965</v>
       </c>
     </row>
@@ -29576,18 +29588,20 @@
       <c r="C3" t="n">
         <v>404258046</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
         <v>25.15</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>programmes</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>404258046</v>
       </c>
     </row>
@@ -29603,18 +29617,20 @@
       <c r="C4" t="n">
         <v>639705043</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>28.36</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>programmes</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>639705043</v>
       </c>
     </row>
@@ -31729,7 +31745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F283"/>
+  <dimension ref="A1:F286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33916,7 +33932,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>no_grand_total</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -33924,19 +33940,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>03000</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>03000.1.99.001</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>program '03000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>the document printed no grand total that stage 5 could find, so there is nothing to check the extraction's completeness against. Every share for FY2019 rests on the heads being all of them.</t>
         </is>
       </c>
     </row>
@@ -33948,27 +33956,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>no_grand_total</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>05000</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>05000.1.99.001</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>program '05000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>the document printed no grand total that stage 5 could find, so there is nothing to check the extraction's completeness against. Every share for FY2022 rests on the heads being all of them.</t>
         </is>
       </c>
     </row>
@@ -33980,27 +33980,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>no_grand_total</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>05000</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>05000.1.99.157</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>program '05000.1.99.157' (Government Audit Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>the document printed no grand total that stage 5 could find, so there is nothing to check the extraction's completeness against. Every share for FY2024 rests on the heads being all of them.</t>
         </is>
       </c>
     </row>
@@ -34022,17 +34014,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>06000</t>
+          <t>03000</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>06000.1.03.001</t>
+          <t>03000.1.99.001</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>program '06000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '03000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34054,17 +34046,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>06000</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>06000.1.03.158</t>
+          <t>05000.1.99.001</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>program '06000.1.03.158' (Public Service Personnel Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '05000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34086,17 +34078,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>07000.1.99.001</t>
+          <t>05000.1.99.157</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>program '07000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '05000.1.99.157' (Government Audit Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34118,17 +34110,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>06000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>07000.1.99.139</t>
+          <t>06000.1.03.001</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>program '07000.1.99.139' (Protection of Children's Rights) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '06000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34150,17 +34142,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>06000</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>07000.1.99.159</t>
+          <t>06000.1.03.158</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>program '07000.1.99.159' (Combatting Human Trafficking) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '06000.1.03.158' (Public Service Personnel Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34182,17 +34174,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15000.6.01.186</t>
+          <t>07000.1.99.001</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>program '15000.6.01.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '07000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34214,17 +34206,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15000.6.99.186</t>
+          <t>07000.1.99.139</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>program '15000.6.99.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '07000.1.99.139' (Protection of Children's Rights) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34246,17 +34238,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16000.1.01.001</t>
+          <t>07000.1.99.159</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>program '16000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '07000.1.99.159' (Combatting Human Trafficking) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34278,17 +34270,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19000.6.01.016</t>
+          <t>15000.6.01.186</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>program '19000.6.01.016' (Investment Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.01.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34310,17 +34302,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19000.6.04.185</t>
+          <t>15000.6.99.186</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>program '19000.6.04.185' (Environmental Management and Climate Change) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.99.186' (Oversight of Assigned Subjects) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34342,17 +34334,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19000.6.06.378</t>
+          <t>16000.1.01.001</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>program '19000.6.06.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '16000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34379,12 +34371,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19000.6.14.177</t>
+          <t>19000.6.01.016</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>program '19000.6.14.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.01.016' (Investment Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34411,12 +34403,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19000.6.99.378</t>
+          <t>19000.6.04.185</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>program '19000.6.99.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.185' (Environmental Management and Climate Change) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34438,17 +34430,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19047.1.01.177</t>
+          <t>19000.6.06.378</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>program '19047.1.01.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34470,17 +34462,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19047.1.03.001</t>
+          <t>19000.6.14.177</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>program '19047.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.14.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34502,17 +34494,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19047.1.03.177</t>
+          <t>19000.6.99.378</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>program '19047.1.03.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.99.378' (Land, Infrastructure and Physical Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34534,17 +34526,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19050.1.06.001</t>
+          <t>19047.1.01.177</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>program '19050.1.06.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19047.1.01.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34566,17 +34558,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19050.1.06.174</t>
+          <t>19047.1.03.001</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>program '19050.1.06.174' (Roads Infrastructure Development and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19047.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34598,17 +34590,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20000.1.02.001</t>
+          <t>19047.1.03.177</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>program '20000.1.02.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19047.1.03.177' (Land Administration and Estate Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34630,17 +34622,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20000.1.02.132</t>
+          <t>19050.1.06.001</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>program '20000.1.02.132' (Macrofiscal Policy and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19050.1.06.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34662,17 +34654,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20000.1.02.137</t>
+          <t>19050.1.06.174</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>program '20000.1.02.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19050.1.06.174' (Roads Infrastructure Development and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34699,12 +34691,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20000.1.03.138</t>
+          <t>20000.1.02.001</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>program '20000.1.03.138' (Public Service Management and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.02.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34731,12 +34723,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20000.1.05.142</t>
+          <t>20000.1.02.132</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>program '20000.1.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.02.132' (Macrofiscal Policy and Management) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34763,12 +34755,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20000.1.99.001</t>
+          <t>20000.1.02.137</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>program '20000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.02.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34795,12 +34787,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20000.1.99.144</t>
+          <t>20000.1.03.138</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>program '20000.1.99.144' (Promotion of the Integrity of Contracts and Licenses) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.03.138' (Public Service Management and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34827,12 +34819,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20000.6.05.142</t>
+          <t>20000.1.05.142</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>program '20000.6.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34859,12 +34851,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20000.6.99.137</t>
+          <t>20000.1.99.001</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>program '20000.6.99.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.99.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34891,12 +34883,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20000.6.99.142</t>
+          <t>20000.1.99.144</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>program '20000.6.99.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.1.99.144' (Promotion of the Integrity of Contracts and Licenses) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34918,17 +34910,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>26000.1.01.436</t>
+          <t>20000.6.05.142</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>program '26000.1.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.05.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34950,17 +34942,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>26000.1.01.437</t>
+          <t>20000.6.99.137</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>program '26000.1.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.99.137' (Management of Public Finances) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -34982,17 +34974,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>26000.6.01.436</t>
+          <t>20000.6.99.142</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>program '26000.6.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.99.142' (Integrated Development Planning) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35019,12 +35011,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>26000.6.01.437</t>
+          <t>26000.1.01.436</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>program '26000.6.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35046,17 +35038,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>26022.1.01.001</t>
+          <t>26000.1.01.437</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>program '26022.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35078,17 +35070,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>26022.1.01.420</t>
+          <t>26000.6.01.436</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>program '26022.1.01.420' (Public Safety and Internal Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.01.436' (Internal Security and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35110,17 +35102,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>26053.1.01.001</t>
+          <t>26000.6.01.437</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>program '26053.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.01.437' (Territorial and Sovereign Protection) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35142,17 +35134,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>26053.1.01.438</t>
+          <t>26022.1.01.001</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>program '26053.1.01.438' (Travel and Identity Facilitation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26022.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35174,17 +35166,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>26059.1.01.001</t>
+          <t>26022.1.01.420</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>program '26059.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26022.1.01.420' (Public Safety and Internal Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35206,17 +35198,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>28030.1.03.001</t>
+          <t>26053.1.01.001</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>program '28030.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26053.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35238,17 +35230,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>28031.1.03.001</t>
+          <t>26053.1.01.438</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>program '28031.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26053.1.01.438' (Travel and Identity Facilitation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35270,17 +35262,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>28058</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>28058.1.03.427</t>
+          <t>26059.1.01.001</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>program '28058.1.03.427' (Administration of Justice) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26059.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35302,17 +35294,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>30000.1.04.001</t>
+          <t>28030.1.03.001</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>program '30000.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28030.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35334,17 +35326,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>28031</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>30000.1.04.150</t>
+          <t>28031.1.03.001</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>program '30000.1.04.150' (Management of Foreign Affairs) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28031.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35366,17 +35358,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>41051.1.04.001</t>
+          <t>28058.1.03.427</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>program '41051.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28058.1.03.427' (Administration of Justice) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35398,17 +35390,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>41051.1.04.326</t>
+          <t>30000.1.04.001</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>program '41051.1.04.326' (Children and Family Welfare Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '30000.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35430,17 +35422,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>42000.1.01.001</t>
+          <t>30000.1.04.150</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>program '42000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '30000.1.04.150' (Management of Foreign Affairs) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35462,17 +35454,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>42000.1.01.282</t>
+          <t>41051.1.04.001</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>program '42000.1.01.282' (Health Sector Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41051.1.04.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35494,17 +35486,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>42000.1.04.281</t>
+          <t>41051.1.04.326</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>program '42000.1.04.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41051.1.04.326' (Children and Family Welfare Services) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35531,12 +35523,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>42000.1.05.281</t>
+          <t>42000.1.01.001</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>program '42000.1.05.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35563,12 +35555,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>42000.6.01.281</t>
+          <t>42000.1.01.282</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>program '42000.6.01.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.01.282' (Health Sector Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35590,17 +35582,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>46000.1.01.001</t>
+          <t>42000.1.04.281</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>program '46000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.04.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35622,17 +35614,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>46000.1.01.268</t>
+          <t>42000.1.05.281</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>program '46000.1.01.268' (Development and Promotion of Sports and Recreation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.05.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35654,17 +35646,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>46000.1.02.265</t>
+          <t>42000.6.01.281</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>program '46000.1.02.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.6.01.281' (Delivery and Management of Health Care) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35691,12 +35683,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>46000.1.03.265</t>
+          <t>46000.1.01.001</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>program '46000.1.03.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35723,12 +35715,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>46000.1.13.267</t>
+          <t>46000.1.01.268</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>program '46000.1.13.267' (Entertainment Economic Linkages) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.01.268' (Development and Promotion of Sports and Recreation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35755,12 +35747,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>46000.1.99.266</t>
+          <t>46000.1.02.265</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>program '46000.1.99.266' (Gender Mainstreaming) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.02.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35782,17 +35774,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>51000.1.03.001</t>
+          <t>46000.1.03.265</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>program '51000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.03.265' (Arts and Culture Preservation and Promotion) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35814,17 +35806,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>51000.1.03.181</t>
+          <t>46000.1.13.267</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>program '51000.1.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.13.267' (Entertainment Economic Linkages) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35846,17 +35838,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>51000.6.03.181</t>
+          <t>46000.1.99.266</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>program '51000.6.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.1.99.266' (Gender Mainstreaming) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35878,17 +35870,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>53000.1.01.182</t>
+          <t>51000.1.03.001</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>program '53000.1.01.182' (Industrial Development and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.03.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35910,17 +35902,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>53000.1.01.184</t>
+          <t>51000.1.03.181</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>program '53000.1.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35942,17 +35934,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>53000.6.01.184</t>
+          <t>51000.6.03.181</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>program '53000.6.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.6.03.181' (Agricultural Production, Productivity and Food Security) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -35974,17 +35966,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>53038.1.01.001</t>
+          <t>53000.1.01.182</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>program '53038.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.182' (Industrial Development and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36006,17 +35998,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>53038.1.01.156</t>
+          <t>53000.1.01.184</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>program '53038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36038,17 +36030,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>72000.1.99.013</t>
+          <t>53000.6.01.184</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>program '72000.1.99.013' (Local Government Oversight) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.6.01.184' (Trade Promotion and Development) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36065,22 +36057,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2019,2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>10000.1.01.001</t>
+          <t>53038.1.01.001</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>program '10000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53038.1.01.001' (Executive Direction and Administration) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36097,22 +36089,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2019,2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>10000.1.99.730</t>
+          <t>53038.1.01.156</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>program '10000.1.99.730' (Independent Oversight of Fiscal Policies and Fiscal Performance) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36129,22 +36121,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2019,2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>15039.1.11.001</t>
+          <t>72000.1.99.013</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>program '15039.1.11.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.013' (Local Government Oversight) exists in ['2022', '2024'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36166,17 +36158,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>15039.1.11.555</t>
+          <t>10000.1.01.001</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>program '15039.1.11.555' (Postal Operations and Courier Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '10000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36198,17 +36190,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>16000.1.01.187</t>
+          <t>10000.1.99.730</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>program '16000.1.01.187' (Public Sector Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '10000.1.99.730' (Independent Oversight of Fiscal Policies and Fiscal Performance) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36230,17 +36222,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19000.1.01.379</t>
+          <t>15039.1.11.001</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>program '19000.1.01.379' (Housing and Urban Renewal) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15039.1.11.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36262,17 +36254,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>19000.1.03.378</t>
+          <t>15039.1.11.555</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>program '19000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15039.1.11.555' (Postal Operations and Courier Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36294,17 +36286,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>19000.1.06.378</t>
+          <t>16000.1.01.187</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>program '19000.1.06.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '16000.1.01.187' (Public Sector Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36331,12 +36323,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>19000.1.14.378</t>
+          <t>19000.1.01.379</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>program '19000.1.14.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.01.379' (Housing and Urban Renewal) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36363,12 +36355,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>19000.1.15.185</t>
+          <t>19000.1.03.378</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>program '19000.1.15.185' (Environmental Management and Climate Change) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36395,12 +36387,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>19000.1.99.001</t>
+          <t>19000.1.06.378</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>program '19000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.06.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36427,12 +36419,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>19000.6.03.378</t>
+          <t>19000.1.14.378</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>program '19000.6.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.14.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36454,17 +36446,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>20000.6.06.137</t>
+          <t>19000.1.15.185</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>program '20000.6.06.137' (Management of Public Finances) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.15.185' (Environmental Management and Climate Change) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36486,17 +36478,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>20011.1.02.47</t>
+          <t>19000.1.99.001</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>program '20011.1.02.47' (Treasury Planning and Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36518,17 +36510,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>20060.1.02.189</t>
+          <t>19000.6.03.378</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>program '20060.1.02.189' (Management of Financial Crimes) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36550,17 +36542,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>20061.1.02.190</t>
+          <t>20000.6.06.137</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>program '20061.1.02.190' (Government Revenue Protection and Compliance Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.06.137' (Management of Public Finances) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36582,17 +36574,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>28058</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>28058.1.03.012</t>
+          <t>20011.1.02.47</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>program '28058.1.03.012' (Judiciary Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20011.1.02.47' (Treasury Planning and Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36614,17 +36606,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>40000.1.01.325</t>
+          <t>20060.1.02.189</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>program '40000.1.01.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20060.1.02.189' (Management of Financial Crimes) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36646,17 +36638,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>40000.1.02.001</t>
+          <t>20061.1.02.190</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>program '40000.1.02.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20061.1.02.190' (Government Revenue Protection and Compliance Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36678,17 +36670,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>40000.1.02.325</t>
+          <t>28058.1.03.012</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>program '40000.1.02.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28058.1.03.012' (Judiciary Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36715,12 +36707,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>40000.1.02.726</t>
+          <t>40000.1.01.325</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>program '40000.1.02.726' ((formerly Promotion and Supervision)) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.01.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36747,12 +36739,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>40000.1.02.729</t>
+          <t>40000.1.02.001</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>program '40000.1.02.729' (National Productivity) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36779,12 +36771,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>40000.1.03.325</t>
+          <t>40000.1.02.325</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>program '40000.1.03.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36811,12 +36803,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>40000.1.99.325</t>
+          <t>40000.1.02.726</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>program '40000.1.99.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.726' ((formerly Promotion and Supervision)) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36843,12 +36835,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>40000.1.99.328</t>
+          <t>40000.1.02.729</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>program '40000.1.99.328' (Social Security Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.02.729' (National Productivity) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36870,17 +36862,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>41000.6.04.261</t>
+          <t>40000.1.03.325</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>program '41000.6.04.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.03.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36902,17 +36894,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>41000.6.06.261</t>
+          <t>40000.1.99.325</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>program '41000.6.06.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.99.325' (Social Welfare Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36934,17 +36926,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>51000.1.05.179</t>
+          <t>40000.1.99.328</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>program '51000.1.05.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '40000.1.99.328' (Social Security Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36966,17 +36958,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>51000.1.15.179</t>
+          <t>41000.6.04.261</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>program '51000.1.15.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.6.04.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -36998,17 +36990,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>53000.1.01.001</t>
+          <t>41000.6.06.261</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>program '53000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.6.06.261' (Education and Training Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37030,17 +37022,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>53000.1.01.183</t>
+          <t>51000.1.05.179</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>program '53000.1.01.183' (Consumer and Public Protection) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.05.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37062,17 +37054,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>69000.1.04.701</t>
+          <t>51000.1.15.179</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>program '69000.1.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51000.1.15.179' (Mineral Sector and Geological Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37094,17 +37086,17 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>69000.1.06.178</t>
+          <t>53000.1.01.001</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>program '69000.1.06.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37126,17 +37118,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>69000.1.07.178</t>
+          <t>53000.1.01.183</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>program '69000.1.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '53000.1.01.183' (Consumer and Public Protection) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37163,12 +37155,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>69000.1.09.178</t>
+          <t>69000.1.04.701</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>program '69000.1.09.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37195,12 +37187,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>69000.1.10.178</t>
+          <t>69000.1.06.178</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>program '69000.1.10.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.06.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37227,12 +37219,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>69000.1.12.128</t>
+          <t>69000.1.07.178</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>program '69000.1.12.128' (ICT Development, Access and Use) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37259,12 +37251,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>69000.1.15.003</t>
+          <t>69000.1.09.178</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>program '69000.1.15.003' (Research and Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.09.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37291,12 +37283,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>69000.1.15.129</t>
+          <t>69000.1.10.178</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>program '69000.1.15.129' (Science, Technology and Innovation Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.10.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37323,12 +37315,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>69000.1.99.001</t>
+          <t>69000.1.12.128</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>program '69000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.12.128' (ICT Development, Access and Use) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37355,12 +37347,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>69000.6.04.701</t>
+          <t>69000.1.15.003</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>program '69000.6.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.15.003' (Research and Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37387,12 +37379,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>69000.6.07.178</t>
+          <t>69000.1.15.129</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>program '69000.6.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.15.129' (Science, Technology and Innovation Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37414,17 +37406,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>72000.1.01.013</t>
+          <t>69000.1.99.001</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>program '72000.1.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37446,17 +37438,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>72000.1.02.014</t>
+          <t>69000.6.04.701</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>program '72000.1.02.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.6.04.701' (Energy Management and Implementation) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37478,17 +37470,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>72000.1.02.015</t>
+          <t>69000.6.07.178</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>program '72000.1.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '69000.6.07.178' (Transport Management and Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37515,12 +37507,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>72000.1.03.378</t>
+          <t>72000.1.01.013</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>program '72000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37547,12 +37539,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>72000.1.06.013</t>
+          <t>72000.1.02.014</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>program '72000.1.06.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.02.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37579,12 +37571,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>72000.1.99.001</t>
+          <t>72000.1.02.015</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>program '72000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37611,12 +37603,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>72000.1.99.014</t>
+          <t>72000.1.03.378</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>program '72000.1.99.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.03.378' (Land, Infrastructure and Physical Development) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37643,12 +37635,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>72000.6.01.013</t>
+          <t>72000.1.06.013</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>program '72000.6.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.06.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37675,12 +37667,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>72000.6.02.015</t>
+          <t>72000.1.99.001</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>program '72000.6.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.001' (Executive Direction and Administration) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37697,22 +37689,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2019,2024</t>
+          <t>2019,2022</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>15010.1.03.001</t>
+          <t>72000.1.99.014</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>program '15010.1.03.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.014' (Community Development and Social Services) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37729,22 +37721,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2019,2024</t>
+          <t>2019,2022</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>15010.1.03.468</t>
+          <t>72000.6.01.013</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>program '15010.1.03.468' (Government Information and Communication Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.6.01.013' (Local Government Oversight) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37761,22 +37753,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2019,2024</t>
+          <t>2019,2022</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>19000.6.04.378</t>
+          <t>72000.6.02.015</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>program '19000.6.04.378' (Land, Infrastructure and Physical Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.6.02.015' (National Disaster Management) exists in ['2024'] but is absent in ['2019', '2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37798,17 +37790,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>20000.6.02.137</t>
+          <t>15010.1.03.001</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>program '20000.6.02.137' (Management of Public Finances) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15010.1.03.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37830,17 +37822,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>26059.1.01.439</t>
+          <t>15010.1.03.468</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>program '26059.1.01.439' (Corruption and Cyber Threat Management) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15010.1.03.468' (Government Information and Communication Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37862,17 +37854,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>27000.1.01.001</t>
+          <t>19000.6.04.378</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>program '27000.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.378' (Land, Infrastructure and Physical Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37894,17 +37886,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>27000.1.01.188</t>
+          <t>20000.6.02.137</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>program '27000.1.01.188' (Facilitation of Law Reform) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20000.6.02.137' (Management of Public Finances) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37926,17 +37918,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>41000.1.22.24</t>
+          <t>26059.1.01.439</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>program '41000.1.22.24' (25) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26059.1.01.439' (Corruption and Cyber Threat Management) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37958,17 +37950,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>42034.1.01.001</t>
+          <t>27000.1.01.001</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>program '42034.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '27000.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -37990,17 +37982,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>42034.1.01.175</t>
+          <t>27000.1.01.188</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>program '42034.1.01.175' (Mental Health Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '27000.1.01.188' (Facilitation of Law Reform) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38022,17 +38014,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>42035.1.01.001</t>
+          <t>41000.1.22.24</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>program '42035.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.22.24' (25) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38054,17 +38046,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>42034</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>42035.1.01.176</t>
+          <t>42034.1.01.001</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>program '42035.1.01.176' (Chemistry Support Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42034.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38086,17 +38078,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42034</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>56000.1.04.701</t>
+          <t>42034.1.01.175</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>program '56000.1.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42034.1.01.175' (Mental Health Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38118,17 +38110,17 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>56000.1.12.128</t>
+          <t>42035.1.01.001</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>program '56000.1.12.128' (ICT Development, Access and Use) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42035.1.01.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38150,17 +38142,17 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>56000.1.15.003</t>
+          <t>42035.1.01.176</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>program '56000.1.15.003' (Research and Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42035.1.01.176' (Chemistry Support Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38187,12 +38179,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>56000.1.15.129</t>
+          <t>56000.1.04.701</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>program '56000.1.15.129' (Science, Technology and Innovation Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38219,12 +38211,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>56000.1.99.001</t>
+          <t>56000.1.12.128</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>program '56000.1.99.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.12.128' (ICT Development, Access and Use) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38251,12 +38243,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>56000.6.04.701</t>
+          <t>56000.1.15.003</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>program '56000.6.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.15.003' (Research and Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38278,17 +38270,17 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>56039.1.11.555</t>
+          <t>56000.1.15.129</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>program '56039.1.11.555' (Postal Operations and Courier Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.15.129' (Science, Technology and Innovation Development) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38305,22 +38297,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019,2024</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>20011.1.02.001</t>
+          <t>56000.1.99.001</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>program '20011.1.02.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.1.99.001' (Executive Direction and Administration) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38337,22 +38329,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019,2024</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>26024.1.04.001</t>
+          <t>56000.6.04.701</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>program '26024.1.04.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.6.04.701' (Energy Management and Implementation) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38369,22 +38361,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2022,2024</t>
+          <t>2019,2024</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>56039</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>15000.6.01.145</t>
+          <t>56039.1.11.555</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>program '15000.6.01.145' (Corporate Office of the Prime Minister) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56039.1.11.555' (Postal Operations and Courier Services) exists in ['2022'] but is absent in ['2019', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38401,22 +38393,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2022,2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>15000.6.04.701</t>
+          <t>20011.1.02.001</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>program '15000.6.04.701' (Energy Conservation and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20011.1.02.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38433,22 +38425,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2022,2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>15000.6.99.011</t>
+          <t>26024.1.04.001</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>program '15000.6.99.011' (Poverty Alleviation Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26024.1.04.001' (Executive Direction and Administration) exists in ['2019', '2024'] but is absent in ['2022'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38470,17 +38462,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>16000.6.99.152</t>
+          <t>15000.6.01.145</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>program '16000.6.99.152' (Public Sector Reform Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.01.145' (Corporate Office of the Prime Minister) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38502,17 +38494,17 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>17000.1.13.001</t>
+          <t>15000.6.04.701</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>program '17000.1.13.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.04.701' (Energy Conservation and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38534,17 +38526,17 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>17000.1.13.652</t>
+          <t>15000.6.99.011</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>program '17000.1.13.652' (Tourism Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '15000.6.99.011' (Poverty Alleviation Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38566,17 +38558,17 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>19000.6.01.301</t>
+          <t>16000.6.99.152</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>program '19000.6.01.301' (Industrial Development and Export Promotion) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '16000.6.99.152' (Public Sector Reform Programme) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38598,17 +38590,17 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>19000.6.03.479</t>
+          <t>17000.1.13.001</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>program '19000.6.03.479' (Surveys and Investigations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '17000.1.13.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38630,17 +38622,17 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>19000.6.03.480</t>
+          <t>17000.1.13.652</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>program '19000.6.03.480' (Rural Water Supply Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '17000.1.13.652' (Tourism Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38667,12 +38659,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>19000.6.04.001</t>
+          <t>19000.6.01.301</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>program '19000.6.04.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.01.301' (Industrial Development and Export Promotion) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38699,12 +38691,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>19000.6.04.625</t>
+          <t>19000.6.03.479</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>program '19000.6.04.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.03.479' (Surveys and Investigations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38731,12 +38723,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>19000.6.06.005</t>
+          <t>19000.6.03.480</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>program '19000.6.06.005' (Disaster Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.03.480' (Rural Water Supply Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38763,12 +38755,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>19000.6.06.225</t>
+          <t>19000.6.04.001</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>program '19000.6.06.225' (Arterial Roads) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38795,12 +38787,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>19000.6.06.228</t>
+          <t>19000.6.04.625</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>program '19000.6.06.228' (Urban Roads, Kingston and St. Andrew) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.04.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38827,12 +38819,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>19000.6.06.377</t>
+          <t>19000.6.06.005</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>program '19000.6.06.377' (Area Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.005' (Disaster Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38859,12 +38851,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>19000.6.14.376</t>
+          <t>19000.6.06.225</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>program '19000.6.14.376' (Land Use Planning and Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.225' (Arterial Roads) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38891,12 +38883,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>19000.6.15.600</t>
+          <t>19000.6.06.228</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>program '19000.6.15.600' (Meteorological, Weather and Climate Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.228' (Urban Roads, Kingston and St. Andrew) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38923,12 +38915,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>19000.6.99.001</t>
+          <t>19000.6.06.377</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>program '19000.6.99.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.06.377' (Area Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38955,12 +38947,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>19000.6.99.625</t>
+          <t>19000.6.14.376</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>program '19000.6.99.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.14.376' (Land Use Planning and Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -38982,17 +38974,17 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>20011.1.02.147</t>
+          <t>19000.6.15.600</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>program '20011.1.02.147' (Treasury Planning and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.15.600' (Meteorological, Weather and Climate Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39014,17 +39006,17 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>20019.1.03.100</t>
+          <t>19000.6.99.001</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>program '20019.1.03.100' (Crop/Livestock) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.99.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39046,17 +39038,17 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>20019.1.08.550</t>
+          <t>19000.6.99.625</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>program '20019.1.08.550' (Railway Operations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '19000.6.99.625' (Protection and Conservation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39078,17 +39070,17 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>26000.1.01.327</t>
+          <t>20011.1.02.147</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>program '26000.1.01.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20011.1.02.147' (Treasury Planning and Management) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39110,17 +39102,17 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>26000.1.01.400</t>
+          <t>20019.1.03.100</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>program '26000.1.01.400' (Defense Forces Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20019.1.03.100' (Crop/Livestock) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39142,17 +39134,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>26000.1.01.425</t>
+          <t>20019.1.08.550</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>program '26000.1.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '20019.1.08.550' (Railway Operations) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39179,12 +39171,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>26000.1.01.426</t>
+          <t>26000.1.01.327</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>program '26000.1.01.426' (Legal Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39211,12 +39203,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>26000.6.01.425</t>
+          <t>26000.1.01.400</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>program '26000.6.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.400' (Defense Forces Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39243,12 +39235,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>26000.6.04.428</t>
+          <t>26000.1.01.425</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>program '26000.6.04.428' (Adult Institutions) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39275,12 +39267,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>26000.6.04.431</t>
+          <t>26000.1.01.426</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>program '26000.6.04.431' (Prevention and Rehabilitation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.1.01.426' (Legal Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39302,17 +39294,17 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>28052.1.03.155</t>
+          <t>26000.6.01.425</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>program '28052.1.03.155' (Law Reforms) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.01.425' (Maintenance of Law and Order) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39334,17 +39326,17 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>28054.1.03.012</t>
+          <t>26000.6.04.428</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>program '28054.1.03.012' (Judiciary Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.04.428' (Adult Institutions) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39366,17 +39358,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>28054.1.03.427</t>
+          <t>26000.6.04.431</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>program '28054.1.03.427' (Administration of Justice) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26000.6.04.431' (Prevention and Rehabilitation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39398,17 +39390,17 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>41000.1.01.001</t>
+          <t>28052.1.03.155</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>program '41000.1.01.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28052.1.03.155' (Law Reforms) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39430,17 +39422,17 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>41000.1.01.007</t>
+          <t>28054.1.03.012</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>program '41000.1.01.007' (School Improvement Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28054.1.03.012' (Judiciary Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39462,17 +39454,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>41000.1.02.250</t>
+          <t>28054.1.03.427</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>program '41000.1.02.250' (Delivery of Early Childhood Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '28054.1.03.427' (Administration of Justice) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39499,12 +39491,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>41000.1.03.251</t>
+          <t>41000.1.01.001</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>program '41000.1.03.251' (Delivery of Primary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.01.001' (Executive Direction and Administration) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39531,12 +39523,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>41000.1.03.465</t>
+          <t>41000.1.01.007</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>program '41000.1.03.465' (Preservation of Official and Other Permanent Records) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.01.007' (School Improvement Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39563,12 +39555,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>41000.1.03.468</t>
+          <t>41000.1.02.250</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>program '41000.1.03.468' (Government Information and Communication Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.02.250' (Delivery of Early Childhood Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39595,12 +39587,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>41000.1.04.252</t>
+          <t>41000.1.03.251</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>program '41000.1.04.252' (Delivery of Secondary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.03.251' (Delivery of Primary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39627,12 +39619,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>41000.1.04.254</t>
+          <t>41000.1.03.465</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>program '41000.1.04.254' (Delivery of Technical/Vocational Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.03.465' (Preservation of Official and Other Permanent Records) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39659,12 +39651,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>41000.1.04.326</t>
+          <t>41000.1.03.468</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>program '41000.1.04.326' (Children and Family Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.03.468' (Government Information and Communication Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39691,12 +39683,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>41000.1.05.253</t>
+          <t>41000.1.04.252</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>program '41000.1.05.253' (Delivery of Tertiary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.04.252' (Delivery of Secondary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39723,12 +39715,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>41000.1.05.256</t>
+          <t>41000.1.04.254</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>program '41000.1.05.256' (Teachers Education and Training) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.04.254' (Delivery of Technical/Vocational Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39755,12 +39747,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>41000.1.05.500</t>
+          <t>41000.1.04.326</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>program '41000.1.05.500' (Youth Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.04.326' (Children and Family Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39787,12 +39779,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>41000.1.06.255</t>
+          <t>41000.1.05.253</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>program '41000.1.06.255' (Delivery of Special Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.05.253' (Delivery of Tertiary Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39819,12 +39811,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>41000.1.07.004</t>
+          <t>41000.1.05.256</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>program '41000.1.07.004' (Regional and International Cooperation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.05.256' (Teachers Education and Training) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39851,12 +39843,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>41000.1.07.258</t>
+          <t>41000.1.05.500</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>program '41000.1.07.258' (Core Educational Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.05.500' (Youth Development) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39883,12 +39875,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>41000.1.07.259</t>
+          <t>41000.1.06.255</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>program '41000.1.07.259' (Library Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.06.255' (Delivery of Special Education) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39915,12 +39907,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>41000.1.07.260</t>
+          <t>41000.1.07.004</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>program '41000.1.07.260' (Nutrition) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.004' (Regional and International Cooperation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39942,17 +39934,17 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>42000.1.05.327</t>
+          <t>41000.1.07.258</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>program '42000.1.05.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.258' (Core Educational Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -39974,17 +39966,17 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>46000.6.99.325</t>
+          <t>41000.1.07.259</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>program '46000.6.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.259' (Library Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40006,17 +39998,17 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>50038.1.01.156</t>
+          <t>41000.1.07.260</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>program '50038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '41000.1.07.260' (Nutrition) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40038,17 +40030,17 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>56000.6.11.128</t>
+          <t>42000.1.05.327</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>program '56000.6.11.128' (ICT Development, Access and Use) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '42000.1.05.327' (Prevention and Control of Drug Abuse) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40070,17 +40062,17 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>68000</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>68000.6.07.178</t>
+          <t>46000.6.99.325</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>program '68000.6.07.178' (Transport Management and Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '46000.6.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40102,17 +40094,17 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>72000.1.99.325</t>
+          <t>50038.1.01.156</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>program '72000.1.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50038.1.01.156' (Business and Personal Property Registration and Regulation) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40129,22 +40121,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022,2024</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>02000</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>02000.1.01.001</t>
+          <t>56000.6.11.128</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>program '02000.1.01.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '56000.6.11.128' (ICT Development, Access and Use) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40161,22 +40153,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022,2024</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>02000</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>02000.1.01.164</t>
+          <t>68000.6.07.178</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>program '02000.1.01.164' (Legislative Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '68000.6.07.178' (Transport Management and Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40193,22 +40185,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022,2024</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>02000</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>02000.1.01.165</t>
+          <t>72000.1.99.325</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>program '02000.1.01.165' (Political and Electoral Dispute Resolution) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '72000.1.99.325' (Social Welfare Services) exists in ['2019'] but is absent in ['2022', '2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40230,17 +40222,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>02000</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>20056.1.02.001</t>
+          <t>02000.1.01.001</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>program '20056.1.02.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '02000.1.01.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40262,17 +40254,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>02000</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>20056.1.02.149</t>
+          <t>02000.1.01.164</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>program '20056.1.02.149' (Domestic Tax Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '02000.1.01.164' (Legislative Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -40294,151 +40286,247 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>02000</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>26000.6.01.400</t>
+          <t>02000.1.01.165</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>program '26000.6.01.400' (Defence Force Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '02000.1.01.165' (Political and Electoral Dispute Resolution) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>large_yoy_swing</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2019-&gt;2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>26000.1.01.001</t>
+          <t>20056.1.02.001</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>program '26000.1.01.001' changed +226% (2,116,532.0 -&gt; 6,902,991.0) - verify this is real and not an extraction error.</t>
+          <t>program '20056.1.02.001' (Executive Direction and Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>large_yoy_swing</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2022-&gt;2024</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>20000.6.99.137</t>
+          <t>20056.1.02.149</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>program '20000.6.99.137' changed +223% (7,603,835.0 -&gt; 24,535,325.0) - verify this is real and not an extraction error.</t>
+          <t>program '20056.1.02.149' (Domestic Tax Administration) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>26000.6.01.400</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>national budget total = 239,480,965.0</t>
+          <t>program '26000.6.01.400' (Defence Force Services) exists in ['2019', '2022'] but is absent in ['2024'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>large_yoy_swing</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
+          <t>2019-&gt;2022</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>26000.1.01.001</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>national budget total = 404,258,046.0</t>
+          <t>program '26000.1.01.001' changed +226% (2,116,532.0 -&gt; 6,902,991.0) - verify this is real and not an extraction error.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>large_yoy_swing</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2022-&gt;2024</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>20000.6.99.137</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>program '20000.6.99.137' changed +223% (7,603,835.0 -&gt; 24,535,325.0) - verify this is real and not an extraction error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>national_total</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>national budget total = 239,480,965.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>national budget total = 404,258,046.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr">
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
         <is>
           <t>national budget total = 639,705,043.0</t>
         </is>
